--- a/预测.xlsx
+++ b/预测.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wenqiang.ding\Desktop\0316\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wenqiang.ding\Desktop\0325\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFBA628C-6619-4BC8-ACD6-E996BDE1502F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{976F2E1C-F47A-44EB-A20E-1AC45A0D582F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Sheet2" sheetId="15" state="hidden" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$I$213</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$I$209</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sheet2!$A$3:$L$221</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1445" uniqueCount="640">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1437" uniqueCount="640">
   <si>
     <t>档位</t>
   </si>
@@ -1569,10 +1569,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>A</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>东部+长电</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1854,10 +1850,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>NM.SC2402UA-GC-00AK</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>3月预测</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1971,6 +1963,12 @@
   </si>
   <si>
     <t>生产料号</t>
+  </si>
+  <si>
+    <t>NM.SC2402UA-GC-00AK</t>
+  </si>
+  <si>
+    <t>SC2498CUA-N-Q-DB-60CK-2498C</t>
   </si>
 </sst>
 </file>
@@ -2363,7 +2361,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2181453-C22C-4113-B8D2-921D754AC68D}">
-  <dimension ref="A1:I368"/>
+  <dimension ref="A1:I364"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.5" bestFit="1" customWidth="1"/>
@@ -2375,16 +2373,16 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E1" s="3" t="s">
         <v>471</v>
@@ -2454,10 +2452,10 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
+        <v>591</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>592</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>593</v>
       </c>
       <c r="C4" s="4"/>
       <c r="D4" s="4"/>
@@ -2479,10 +2477,10 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
@@ -2507,7 +2505,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
@@ -2557,7 +2555,7 @@
         <v>5</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>
@@ -2736,7 +2734,7 @@
         <v>10</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
@@ -2834,7 +2832,7 @@
         <v>13</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C19" s="4"/>
       <c r="D19" s="4"/>
@@ -2859,7 +2857,7 @@
         <v>13</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C20" s="4"/>
       <c r="D20" s="4"/>
@@ -2909,7 +2907,7 @@
         <v>270</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="C22" s="4"/>
       <c r="D22" s="4"/>
@@ -3162,7 +3160,7 @@
         <v>29</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>508</v>
+        <v>8</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="6">
@@ -3311,7 +3309,7 @@
         <v>38</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="C38" s="4"/>
       <c r="D38" s="4"/>
@@ -3461,7 +3459,7 @@
         <v>44</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>601</v>
+        <v>638</v>
       </c>
       <c r="C44" s="4"/>
       <c r="D44" s="4"/>
@@ -3686,7 +3684,7 @@
         <v>58</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C53" s="4"/>
       <c r="D53" s="4"/>
@@ -3711,7 +3709,7 @@
         <v>58</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="C54" s="4"/>
       <c r="D54" s="4"/>
@@ -4236,7 +4234,7 @@
         <v>89</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C75" s="4"/>
       <c r="D75" s="4"/>
@@ -4386,7 +4384,7 @@
         <v>93</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C81" s="4"/>
       <c r="D81" s="4"/>
@@ -4411,7 +4409,7 @@
         <v>93</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="C82" s="4"/>
       <c r="D82" s="4"/>
@@ -4686,7 +4684,7 @@
         <v>111</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>486</v>
+        <v>639</v>
       </c>
       <c r="C93" s="4"/>
       <c r="D93" s="4"/>
@@ -4711,7 +4709,7 @@
         <v>111</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C94" s="4"/>
       <c r="D94" s="4"/>
@@ -4736,7 +4734,7 @@
         <v>112</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="C95" s="4"/>
       <c r="D95" s="4"/>
@@ -5086,7 +5084,7 @@
         <v>131</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C109" s="4"/>
       <c r="D109" s="4"/>
@@ -5483,10 +5481,10 @@
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A125" s="4" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="C125" s="4"/>
       <c r="D125" s="4"/>
@@ -5608,10 +5606,10 @@
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A130" s="4" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B130" s="4" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="C130" s="4"/>
       <c r="D130" s="4"/>
@@ -5666,16 +5664,16 @@
       <c r="C132" s="4"/>
       <c r="D132" s="4"/>
       <c r="E132" s="6">
-        <v>90000</v>
+        <v>150000</v>
       </c>
       <c r="F132" s="6">
-        <v>90000</v>
+        <v>150000</v>
       </c>
       <c r="G132" s="6">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="H132" s="6">
-        <v>120000</v>
+        <v>150000</v>
       </c>
       <c r="I132" s="6">
         <v>150000</v>
@@ -5686,7 +5684,7 @@
         <v>166</v>
       </c>
       <c r="B133" s="4" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="C133" s="4"/>
       <c r="D133" s="4"/>
@@ -5711,7 +5709,7 @@
         <v>167</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="C134" s="4"/>
       <c r="D134" s="4"/>
@@ -5791,19 +5789,19 @@
       <c r="C137" s="4"/>
       <c r="D137" s="4"/>
       <c r="E137" s="6">
-        <v>1000</v>
+        <v>100000</v>
       </c>
       <c r="F137" s="6">
-        <v>1000</v>
+        <v>100000</v>
       </c>
       <c r="G137" s="6">
-        <v>5000</v>
+        <v>100000</v>
       </c>
       <c r="H137" s="6">
-        <v>5000</v>
+        <v>100000</v>
       </c>
       <c r="I137" s="6">
-        <v>5000</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.2">
@@ -5811,7 +5809,7 @@
         <v>172</v>
       </c>
       <c r="B138" s="4" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="C138" s="4"/>
       <c r="D138" s="4"/>
@@ -5861,7 +5859,7 @@
         <v>175</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="C140" s="4"/>
       <c r="D140" s="4"/>
@@ -5986,7 +5984,7 @@
         <v>179</v>
       </c>
       <c r="B145" s="4" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="C145" s="4"/>
       <c r="D145" s="4"/>
@@ -6133,85 +6131,85 @@
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A151" s="4" t="s">
-        <v>574</v>
+        <v>622</v>
       </c>
       <c r="B151" s="4" t="s">
-        <v>574</v>
+        <v>623</v>
       </c>
       <c r="C151" s="4"/>
       <c r="D151" s="4"/>
       <c r="E151" s="6">
-        <v>25000</v>
+        <v>40000</v>
       </c>
       <c r="F151" s="6">
-        <v>25000</v>
+        <v>40000</v>
       </c>
       <c r="G151" s="6">
-        <v>25000</v>
+        <v>40000</v>
       </c>
       <c r="H151" s="6">
-        <v>25000</v>
+        <v>40000</v>
       </c>
       <c r="I151" s="6">
-        <v>15000</v>
+        <v>40000</v>
       </c>
     </row>
     <row r="152" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A152" s="4" t="s">
-        <v>594</v>
+        <v>307</v>
       </c>
       <c r="B152" s="4" t="s">
-        <v>594</v>
+        <v>308</v>
       </c>
       <c r="C152" s="4"/>
       <c r="D152" s="4"/>
       <c r="E152" s="6">
-        <v>3000</v>
+        <v>50000</v>
       </c>
       <c r="F152" s="6">
-        <v>3000</v>
+        <v>70000</v>
       </c>
       <c r="G152" s="6">
-        <v>3000</v>
+        <v>70000</v>
       </c>
       <c r="H152" s="6">
-        <v>3000</v>
+        <v>60000</v>
       </c>
       <c r="I152" s="6">
-        <v>3000</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="153" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A153" s="4" t="s">
-        <v>307</v>
+        <v>192</v>
       </c>
       <c r="B153" s="4" t="s">
-        <v>308</v>
+        <v>280</v>
       </c>
       <c r="C153" s="4"/>
       <c r="D153" s="4"/>
       <c r="E153" s="6">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="F153" s="6">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="G153" s="6">
-        <v>0</v>
+        <v>66000</v>
       </c>
       <c r="H153" s="6">
-        <v>0</v>
+        <v>116000</v>
       </c>
       <c r="I153" s="6">
-        <v>0</v>
+        <v>66000</v>
       </c>
     </row>
     <row r="154" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A154" s="4" t="s">
-        <v>572</v>
+        <v>193</v>
       </c>
       <c r="B154" s="4" t="s">
-        <v>572</v>
+        <v>194</v>
       </c>
       <c r="C154" s="4"/>
       <c r="D154" s="4"/>
@@ -6222,271 +6220,271 @@
         <v>0</v>
       </c>
       <c r="G154" s="6">
-        <v>4000</v>
+        <v>30000</v>
       </c>
       <c r="H154" s="6">
         <v>0</v>
       </c>
       <c r="I154" s="6">
-        <v>4000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="155" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A155" s="4" t="s">
-        <v>568</v>
+        <v>193</v>
       </c>
       <c r="B155" s="4" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="C155" s="4"/>
       <c r="D155" s="4"/>
       <c r="E155" s="6">
-        <v>50000</v>
+        <v>1000</v>
       </c>
       <c r="F155" s="6">
-        <v>70000</v>
+        <v>1000</v>
       </c>
       <c r="G155" s="6">
-        <v>70000</v>
+        <v>1000</v>
       </c>
       <c r="H155" s="6">
-        <v>60000</v>
+        <v>1000</v>
       </c>
       <c r="I155" s="6">
-        <v>60000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="156" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A156" s="4" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="B156" s="4" t="s">
-        <v>576</v>
+        <v>196</v>
       </c>
       <c r="C156" s="4"/>
       <c r="D156" s="4"/>
       <c r="E156" s="6">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="F156" s="6">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="G156" s="6">
-        <v>60000</v>
+        <v>4000</v>
       </c>
       <c r="H156" s="6">
-        <v>110000</v>
+        <v>8000</v>
       </c>
       <c r="I156" s="6">
-        <v>60000</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="157" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A157" s="4" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="B157" s="4" t="s">
-        <v>280</v>
+        <v>198</v>
       </c>
       <c r="C157" s="4"/>
       <c r="D157" s="4"/>
       <c r="E157" s="6">
-        <v>6000</v>
+        <v>11000</v>
       </c>
       <c r="F157" s="6">
-        <v>6000</v>
+        <v>11000</v>
       </c>
       <c r="G157" s="6">
-        <v>6000</v>
+        <v>26000</v>
       </c>
       <c r="H157" s="6">
-        <v>6000</v>
+        <v>28000</v>
       </c>
       <c r="I157" s="6">
-        <v>6000</v>
+        <v>31000</v>
       </c>
     </row>
     <row r="158" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A158" s="4" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="B158" s="4" t="s">
-        <v>194</v>
+        <v>281</v>
       </c>
       <c r="C158" s="4"/>
       <c r="D158" s="4"/>
       <c r="E158" s="6">
-        <v>0</v>
+        <v>9000</v>
       </c>
       <c r="F158" s="6">
-        <v>0</v>
+        <v>21000</v>
       </c>
       <c r="G158" s="6">
-        <v>30000</v>
+        <v>28000</v>
       </c>
       <c r="H158" s="6">
-        <v>0</v>
+        <v>26000</v>
       </c>
       <c r="I158" s="6">
-        <v>0</v>
+        <v>34000</v>
       </c>
     </row>
     <row r="159" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A159" s="4" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="B159" s="4" t="s">
-        <v>570</v>
+        <v>201</v>
       </c>
       <c r="C159" s="4"/>
       <c r="D159" s="4"/>
       <c r="E159" s="6">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="F159" s="6">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="G159" s="6">
-        <v>1000</v>
+        <v>3000</v>
       </c>
       <c r="H159" s="6">
-        <v>1000</v>
+        <v>3000</v>
       </c>
       <c r="I159" s="6">
-        <v>1000</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="160" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A160" s="4" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="B160" s="4" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="C160" s="4"/>
       <c r="D160" s="4"/>
       <c r="E160" s="6">
-        <v>4000</v>
+        <v>117000</v>
       </c>
       <c r="F160" s="6">
-        <v>4000</v>
+        <v>88000</v>
       </c>
       <c r="G160" s="6">
-        <v>4000</v>
+        <v>120000</v>
       </c>
       <c r="H160" s="6">
-        <v>8000</v>
+        <v>113000</v>
       </c>
       <c r="I160" s="6">
-        <v>8000</v>
+        <v>113000</v>
       </c>
     </row>
     <row r="161" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A161" s="4" t="s">
-        <v>197</v>
+        <v>282</v>
       </c>
       <c r="B161" s="4" t="s">
-        <v>198</v>
+        <v>283</v>
       </c>
       <c r="C161" s="4"/>
       <c r="D161" s="4"/>
       <c r="E161" s="6">
-        <v>11000</v>
+        <v>0</v>
       </c>
       <c r="F161" s="6">
-        <v>11000</v>
+        <v>500</v>
       </c>
       <c r="G161" s="6">
-        <v>26000</v>
+        <v>0</v>
       </c>
       <c r="H161" s="6">
-        <v>28000</v>
+        <v>4000</v>
       </c>
       <c r="I161" s="6">
-        <v>31000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="162" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A162" s="4" t="s">
-        <v>199</v>
+        <v>584</v>
       </c>
       <c r="B162" s="4" t="s">
-        <v>281</v>
+        <v>583</v>
       </c>
       <c r="C162" s="4"/>
       <c r="D162" s="4"/>
       <c r="E162" s="6">
-        <v>9000</v>
+        <v>0</v>
       </c>
       <c r="F162" s="6">
-        <v>21000</v>
+        <v>0</v>
       </c>
       <c r="G162" s="6">
-        <v>28000</v>
+        <v>0</v>
       </c>
       <c r="H162" s="6">
-        <v>26000</v>
+        <v>11000</v>
       </c>
       <c r="I162" s="6">
-        <v>34000</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="163" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A163" s="4" t="s">
-        <v>200</v>
+        <v>578</v>
       </c>
       <c r="B163" s="4" t="s">
-        <v>201</v>
+        <v>577</v>
       </c>
       <c r="C163" s="4"/>
       <c r="D163" s="4"/>
       <c r="E163" s="6">
-        <v>0</v>
+        <v>2600</v>
       </c>
       <c r="F163" s="6">
-        <v>0</v>
+        <v>2600</v>
       </c>
       <c r="G163" s="6">
-        <v>3000</v>
+        <v>2600</v>
       </c>
       <c r="H163" s="6">
-        <v>3000</v>
+        <v>2600</v>
       </c>
       <c r="I163" s="6">
-        <v>3000</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="164" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A164" s="4" t="s">
-        <v>202</v>
+        <v>581</v>
       </c>
       <c r="B164" s="4" t="s">
-        <v>203</v>
+        <v>580</v>
       </c>
       <c r="C164" s="4"/>
       <c r="D164" s="4"/>
       <c r="E164" s="6">
-        <v>117000</v>
+        <v>0</v>
       </c>
       <c r="F164" s="6">
-        <v>88000</v>
+        <v>2600</v>
       </c>
       <c r="G164" s="6">
-        <v>120000</v>
+        <v>2600</v>
       </c>
       <c r="H164" s="6">
-        <v>113000</v>
+        <v>2600</v>
       </c>
       <c r="I164" s="6">
-        <v>113000</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="165" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A165" s="4" t="s">
-        <v>282</v>
+        <v>204</v>
       </c>
       <c r="B165" s="4" t="s">
-        <v>283</v>
+        <v>205</v>
       </c>
       <c r="C165" s="4"/>
       <c r="D165" s="4"/>
@@ -6494,749 +6492,749 @@
         <v>0</v>
       </c>
       <c r="F165" s="6">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="G165" s="6">
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="H165" s="6">
-        <v>4000</v>
+        <v>6000</v>
       </c>
       <c r="I165" s="6">
-        <v>0</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="166" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A166" s="4" t="s">
-        <v>585</v>
+        <v>206</v>
       </c>
       <c r="B166" s="4" t="s">
-        <v>584</v>
+        <v>209</v>
       </c>
       <c r="C166" s="4"/>
       <c r="D166" s="4"/>
       <c r="E166" s="6">
-        <v>0</v>
+        <v>117000</v>
       </c>
       <c r="F166" s="6">
-        <v>0</v>
+        <v>127000</v>
       </c>
       <c r="G166" s="6">
-        <v>0</v>
+        <v>99000</v>
       </c>
       <c r="H166" s="6">
-        <v>11000</v>
+        <v>102000</v>
       </c>
       <c r="I166" s="6">
-        <v>18000</v>
+        <v>104000</v>
       </c>
     </row>
     <row r="167" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A167" s="4" t="s">
-        <v>579</v>
+        <v>206</v>
       </c>
       <c r="B167" s="4" t="s">
-        <v>578</v>
+        <v>207</v>
       </c>
       <c r="C167" s="4"/>
       <c r="D167" s="4"/>
       <c r="E167" s="6">
-        <v>2600</v>
+        <v>0</v>
       </c>
       <c r="F167" s="6">
-        <v>2600</v>
+        <v>200000</v>
       </c>
       <c r="G167" s="6">
-        <v>2600</v>
+        <v>0</v>
       </c>
       <c r="H167" s="6">
-        <v>2600</v>
+        <v>200000</v>
       </c>
       <c r="I167" s="6">
-        <v>2600</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="168" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A168" s="4" t="s">
-        <v>582</v>
+        <v>206</v>
       </c>
       <c r="B168" s="4" t="s">
-        <v>581</v>
+        <v>208</v>
       </c>
       <c r="C168" s="4"/>
       <c r="D168" s="4"/>
       <c r="E168" s="6">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="F168" s="6">
-        <v>2600</v>
+        <v>10000</v>
       </c>
       <c r="G168" s="6">
-        <v>2600</v>
+        <v>10000</v>
       </c>
       <c r="H168" s="6">
-        <v>2600</v>
+        <v>10000</v>
       </c>
       <c r="I168" s="6">
-        <v>2600</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="169" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A169" s="4" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="B169" s="4" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="C169" s="4"/>
       <c r="D169" s="4"/>
       <c r="E169" s="6">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="F169" s="6">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="G169" s="6">
-        <v>6000</v>
+        <v>4000</v>
       </c>
       <c r="H169" s="6">
-        <v>6000</v>
+        <v>3000</v>
       </c>
       <c r="I169" s="6">
-        <v>6000</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="170" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A170" s="4" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="B170" s="4" t="s">
-        <v>209</v>
+        <v>499</v>
       </c>
       <c r="C170" s="4"/>
       <c r="D170" s="4"/>
       <c r="E170" s="6">
-        <v>117000</v>
+        <v>61000</v>
       </c>
       <c r="F170" s="6">
-        <v>127000</v>
+        <v>46000</v>
       </c>
       <c r="G170" s="6">
-        <v>99000</v>
+        <v>46000</v>
       </c>
       <c r="H170" s="6">
-        <v>102000</v>
+        <v>41000</v>
       </c>
       <c r="I170" s="6">
-        <v>104000</v>
+        <v>57000</v>
       </c>
     </row>
     <row r="171" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A171" s="4" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="B171" s="4" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C171" s="4"/>
       <c r="D171" s="4"/>
       <c r="E171" s="6">
-        <v>0</v>
+        <v>307000</v>
       </c>
       <c r="F171" s="6">
         <v>200000</v>
       </c>
       <c r="G171" s="6">
-        <v>0</v>
+        <v>187000</v>
       </c>
       <c r="H171" s="6">
-        <v>200000</v>
+        <v>178000</v>
       </c>
       <c r="I171" s="6">
-        <v>100000</v>
+        <v>177000</v>
       </c>
     </row>
     <row r="172" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A172" s="4" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="B172" s="4" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="C172" s="4"/>
       <c r="D172" s="4"/>
       <c r="E172" s="6">
-        <v>10000</v>
+        <v>90000</v>
       </c>
       <c r="F172" s="6">
-        <v>10000</v>
+        <v>70000</v>
       </c>
       <c r="G172" s="6">
-        <v>10000</v>
+        <v>70000</v>
       </c>
       <c r="H172" s="6">
-        <v>10000</v>
+        <v>85000</v>
       </c>
       <c r="I172" s="6">
-        <v>10000</v>
+        <v>75000</v>
       </c>
     </row>
     <row r="173" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A173" s="4" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="B173" s="4" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="C173" s="4"/>
       <c r="D173" s="4"/>
       <c r="E173" s="6">
-        <v>4000</v>
+        <v>20000</v>
       </c>
       <c r="F173" s="6">
-        <v>3000</v>
+        <v>20000</v>
       </c>
       <c r="G173" s="6">
-        <v>4000</v>
+        <v>30000</v>
       </c>
       <c r="H173" s="6">
-        <v>3000</v>
+        <v>30000</v>
       </c>
       <c r="I173" s="6">
-        <v>3000</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="174" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A174" s="4" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="B174" s="4" t="s">
-        <v>499</v>
+        <v>220</v>
       </c>
       <c r="C174" s="4"/>
       <c r="D174" s="4"/>
       <c r="E174" s="6">
-        <v>61000</v>
+        <v>10000</v>
       </c>
       <c r="F174" s="6">
-        <v>46000</v>
+        <v>20000</v>
       </c>
       <c r="G174" s="6">
-        <v>46000</v>
+        <v>20000</v>
       </c>
       <c r="H174" s="6">
-        <v>41000</v>
+        <v>10000</v>
       </c>
       <c r="I174" s="6">
-        <v>57000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="175" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A175" s="4" t="s">
-        <v>213</v>
+        <v>587</v>
       </c>
       <c r="B175" s="4" t="s">
-        <v>214</v>
+        <v>586</v>
       </c>
       <c r="C175" s="4"/>
       <c r="D175" s="4"/>
       <c r="E175" s="6">
-        <v>307000</v>
+        <v>0</v>
       </c>
       <c r="F175" s="6">
-        <v>200000</v>
+        <v>1000000</v>
       </c>
       <c r="G175" s="6">
-        <v>187000</v>
+        <v>1000000</v>
       </c>
       <c r="H175" s="6">
-        <v>178000</v>
+        <v>1000000</v>
       </c>
       <c r="I175" s="6">
-        <v>177000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="176" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A176" s="4" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="B176" s="4" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="C176" s="4"/>
       <c r="D176" s="4"/>
       <c r="E176" s="6">
-        <v>90000</v>
+        <v>1500</v>
       </c>
       <c r="F176" s="6">
-        <v>70000</v>
+        <v>2000</v>
       </c>
       <c r="G176" s="6">
-        <v>70000</v>
+        <v>2000</v>
       </c>
       <c r="H176" s="6">
-        <v>85000</v>
+        <v>2000</v>
       </c>
       <c r="I176" s="6">
-        <v>75000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="177" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A177" s="4" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="B177" s="4" t="s">
-        <v>218</v>
+        <v>284</v>
       </c>
       <c r="C177" s="4"/>
       <c r="D177" s="4"/>
       <c r="E177" s="6">
-        <v>20000</v>
+        <v>50000</v>
       </c>
       <c r="F177" s="6">
-        <v>20000</v>
+        <v>50000</v>
       </c>
       <c r="G177" s="6">
-        <v>30000</v>
+        <v>50000</v>
       </c>
       <c r="H177" s="6">
-        <v>30000</v>
+        <v>50000</v>
       </c>
       <c r="I177" s="6">
-        <v>30000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="178" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A178" s="4" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="B178" s="4" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="C178" s="4"/>
       <c r="D178" s="4"/>
       <c r="E178" s="6">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="F178" s="6">
-        <v>20000</v>
+        <v>350000</v>
       </c>
       <c r="G178" s="6">
-        <v>20000</v>
+        <v>300000</v>
       </c>
       <c r="H178" s="6">
-        <v>10000</v>
+        <v>300000</v>
       </c>
       <c r="I178" s="6">
-        <v>10000</v>
+        <v>300000</v>
       </c>
     </row>
     <row r="179" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A179" s="4" t="s">
-        <v>588</v>
+        <v>225</v>
       </c>
       <c r="B179" s="4" t="s">
-        <v>587</v>
+        <v>285</v>
       </c>
       <c r="C179" s="4"/>
       <c r="D179" s="4"/>
       <c r="E179" s="6">
-        <v>0</v>
+        <v>159000</v>
       </c>
       <c r="F179" s="6">
-        <v>1000000</v>
+        <v>416000</v>
       </c>
       <c r="G179" s="6">
-        <v>1000000</v>
+        <v>476000</v>
       </c>
       <c r="H179" s="6">
-        <v>1000000</v>
+        <v>446000</v>
       </c>
       <c r="I179" s="6">
-        <v>0</v>
+        <v>446000</v>
       </c>
     </row>
     <row r="180" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A180" s="4" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="B180" s="4" t="s">
-        <v>222</v>
+        <v>286</v>
       </c>
       <c r="C180" s="4"/>
       <c r="D180" s="4"/>
       <c r="E180" s="6">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="F180" s="6">
-        <v>2000</v>
+        <v>175000</v>
       </c>
       <c r="G180" s="6">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="H180" s="6">
-        <v>2000</v>
+        <v>175000</v>
       </c>
       <c r="I180" s="6">
-        <v>2000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="181" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A181" s="4" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="B181" s="4" t="s">
-        <v>284</v>
+        <v>227</v>
       </c>
       <c r="C181" s="4"/>
       <c r="D181" s="4"/>
       <c r="E181" s="6">
-        <v>50000</v>
+        <v>450000</v>
       </c>
       <c r="F181" s="6">
-        <v>50000</v>
+        <v>450000</v>
       </c>
       <c r="G181" s="6">
-        <v>50000</v>
+        <v>450000</v>
       </c>
       <c r="H181" s="6">
-        <v>50000</v>
+        <v>450000</v>
       </c>
       <c r="I181" s="6">
-        <v>50000</v>
+        <v>450000</v>
       </c>
     </row>
     <row r="182" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A182" s="4" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B182" s="4" t="s">
-        <v>224</v>
+        <v>287</v>
       </c>
       <c r="C182" s="4"/>
       <c r="D182" s="4"/>
       <c r="E182" s="6">
-        <v>0</v>
+        <v>175000</v>
       </c>
       <c r="F182" s="6">
-        <v>350000</v>
+        <v>0</v>
       </c>
       <c r="G182" s="6">
-        <v>300000</v>
+        <v>0</v>
       </c>
       <c r="H182" s="6">
-        <v>300000</v>
+        <v>0</v>
       </c>
       <c r="I182" s="6">
-        <v>300000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="183" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A183" s="4" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="B183" s="4" t="s">
-        <v>285</v>
+        <v>229</v>
       </c>
       <c r="C183" s="4"/>
       <c r="D183" s="4"/>
       <c r="E183" s="6">
-        <v>159000</v>
+        <v>0</v>
       </c>
       <c r="F183" s="6">
-        <v>416000</v>
+        <v>105000</v>
       </c>
       <c r="G183" s="6">
-        <v>476000</v>
+        <v>105000</v>
       </c>
       <c r="H183" s="6">
-        <v>446000</v>
+        <v>105000</v>
       </c>
       <c r="I183" s="6">
-        <v>446000</v>
+        <v>105000</v>
       </c>
     </row>
     <row r="184" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A184" s="4" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B184" s="4" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="C184" s="4"/>
       <c r="D184" s="4"/>
       <c r="E184" s="6">
-        <v>0</v>
+        <v>60000</v>
       </c>
       <c r="F184" s="6">
-        <v>175000</v>
+        <v>60000</v>
       </c>
       <c r="G184" s="6">
-        <v>0</v>
+        <v>60000</v>
       </c>
       <c r="H184" s="6">
-        <v>175000</v>
+        <v>60000</v>
       </c>
       <c r="I184" s="6">
-        <v>0</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="185" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A185" s="4" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B185" s="4" t="s">
-        <v>227</v>
+        <v>288</v>
       </c>
       <c r="C185" s="4"/>
       <c r="D185" s="4"/>
       <c r="E185" s="6">
-        <v>450000</v>
+        <v>0</v>
       </c>
       <c r="F185" s="6">
-        <v>450000</v>
+        <v>0</v>
       </c>
       <c r="G185" s="6">
-        <v>450000</v>
+        <v>0</v>
       </c>
       <c r="H185" s="6">
-        <v>450000</v>
+        <v>80000</v>
       </c>
       <c r="I185" s="6">
-        <v>450000</v>
+        <v>80000</v>
       </c>
     </row>
     <row r="186" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A186" s="4" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="B186" s="4" t="s">
-        <v>287</v>
+        <v>231</v>
       </c>
       <c r="C186" s="4"/>
       <c r="D186" s="4"/>
       <c r="E186" s="6">
-        <v>175000</v>
+        <v>45000</v>
       </c>
       <c r="F186" s="6">
-        <v>0</v>
+        <v>105000</v>
       </c>
       <c r="G186" s="6">
-        <v>0</v>
+        <v>120000</v>
       </c>
       <c r="H186" s="6">
-        <v>0</v>
+        <v>105000</v>
       </c>
       <c r="I186" s="6">
-        <v>0</v>
+        <v>81000</v>
       </c>
     </row>
     <row r="187" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A187" s="4" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B187" s="4" t="s">
-        <v>229</v>
+        <v>290</v>
       </c>
       <c r="C187" s="4"/>
       <c r="D187" s="4"/>
       <c r="E187" s="6">
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="F187" s="6">
-        <v>105000</v>
+        <v>6000</v>
       </c>
       <c r="G187" s="6">
-        <v>105000</v>
+        <v>6000</v>
       </c>
       <c r="H187" s="6">
-        <v>105000</v>
+        <v>16000</v>
       </c>
       <c r="I187" s="6">
-        <v>105000</v>
+        <v>16000</v>
       </c>
     </row>
     <row r="188" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A188" s="4" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="B188" s="4" t="s">
-        <v>289</v>
+        <v>232</v>
       </c>
       <c r="C188" s="4"/>
       <c r="D188" s="4"/>
       <c r="E188" s="6">
-        <v>60000</v>
+        <v>99000</v>
       </c>
       <c r="F188" s="6">
-        <v>60000</v>
+        <v>82500</v>
       </c>
       <c r="G188" s="6">
-        <v>60000</v>
+        <v>126000</v>
       </c>
       <c r="H188" s="6">
-        <v>60000</v>
+        <v>129000</v>
       </c>
       <c r="I188" s="6">
-        <v>60000</v>
+        <v>99000</v>
       </c>
     </row>
     <row r="189" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A189" s="4" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="B189" s="4" t="s">
-        <v>288</v>
+        <v>234</v>
       </c>
       <c r="C189" s="4"/>
       <c r="D189" s="4"/>
       <c r="E189" s="6">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="F189" s="6">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="G189" s="6">
-        <v>0</v>
+        <v>120000</v>
       </c>
       <c r="H189" s="6">
-        <v>80000</v>
+        <v>120000</v>
       </c>
       <c r="I189" s="6">
-        <v>80000</v>
+        <v>90000</v>
       </c>
     </row>
     <row r="190" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A190" s="4" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="B190" s="4" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="C190" s="4"/>
       <c r="D190" s="4"/>
       <c r="E190" s="6">
-        <v>45000</v>
+        <v>523000</v>
       </c>
       <c r="F190" s="6">
-        <v>105000</v>
+        <v>550000</v>
       </c>
       <c r="G190" s="6">
-        <v>120000</v>
+        <v>513000</v>
       </c>
       <c r="H190" s="6">
-        <v>105000</v>
+        <v>540000</v>
       </c>
       <c r="I190" s="6">
-        <v>81000</v>
+        <v>673000</v>
       </c>
     </row>
     <row r="191" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A191" s="4" t="s">
-        <v>230</v>
+        <v>500</v>
       </c>
       <c r="B191" s="4" t="s">
-        <v>290</v>
+        <v>502</v>
       </c>
       <c r="C191" s="4"/>
       <c r="D191" s="4"/>
       <c r="E191" s="6">
-        <v>6000</v>
+        <v>0</v>
       </c>
       <c r="F191" s="6">
-        <v>6000</v>
+        <v>1500</v>
       </c>
       <c r="G191" s="6">
-        <v>6000</v>
+        <v>1500</v>
       </c>
       <c r="H191" s="6">
-        <v>16000</v>
+        <v>1500</v>
       </c>
       <c r="I191" s="6">
-        <v>16000</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="192" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A192" s="4" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="B192" s="4" t="s">
-        <v>232</v>
+        <v>309</v>
       </c>
       <c r="C192" s="4"/>
       <c r="D192" s="4"/>
       <c r="E192" s="6">
-        <v>99000</v>
+        <v>0</v>
       </c>
       <c r="F192" s="6">
-        <v>82500</v>
+        <v>5000</v>
       </c>
       <c r="G192" s="6">
-        <v>126000</v>
+        <v>5000</v>
       </c>
       <c r="H192" s="6">
-        <v>129000</v>
+        <v>5000</v>
       </c>
       <c r="I192" s="6">
-        <v>99000</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="193" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A193" s="4" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="B193" s="4" t="s">
-        <v>234</v>
+        <v>310</v>
       </c>
       <c r="C193" s="4"/>
       <c r="D193" s="4"/>
       <c r="E193" s="6">
-        <v>150000</v>
+        <v>20000</v>
       </c>
       <c r="F193" s="6">
-        <v>150000</v>
+        <v>20500</v>
       </c>
       <c r="G193" s="6">
-        <v>120000</v>
+        <v>20000</v>
       </c>
       <c r="H193" s="6">
-        <v>120000</v>
+        <v>20000</v>
       </c>
       <c r="I193" s="6">
-        <v>90000</v>
+        <v>21000</v>
       </c>
     </row>
     <row r="194" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A194" s="4" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="B194" s="4" t="s">
-        <v>236</v>
+        <v>311</v>
       </c>
       <c r="C194" s="4"/>
       <c r="D194" s="4"/>
       <c r="E194" s="6">
-        <v>523000</v>
+        <v>20000</v>
       </c>
       <c r="F194" s="6">
-        <v>550000</v>
+        <v>22000</v>
       </c>
       <c r="G194" s="6">
-        <v>513000</v>
+        <v>32000</v>
       </c>
       <c r="H194" s="6">
-        <v>540000</v>
+        <v>22000</v>
       </c>
       <c r="I194" s="6">
-        <v>673000</v>
+        <v>32000</v>
       </c>
     </row>
     <row r="195" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A195" s="4" t="s">
-        <v>500</v>
+        <v>240</v>
       </c>
       <c r="B195" s="4" t="s">
-        <v>502</v>
+        <v>241</v>
       </c>
       <c r="C195" s="4"/>
       <c r="D195" s="4"/>
@@ -7244,149 +7242,149 @@
         <v>0</v>
       </c>
       <c r="F195" s="6">
-        <v>1500</v>
+        <v>5000</v>
       </c>
       <c r="G195" s="6">
-        <v>1500</v>
+        <v>5000</v>
       </c>
       <c r="H195" s="6">
-        <v>1500</v>
+        <v>5000</v>
       </c>
       <c r="I195" s="6">
-        <v>1500</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="196" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A196" s="4" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="B196" s="4" t="s">
-        <v>309</v>
+        <v>504</v>
       </c>
       <c r="C196" s="4"/>
       <c r="D196" s="4"/>
       <c r="E196" s="6">
-        <v>0</v>
+        <v>24000</v>
       </c>
       <c r="F196" s="6">
-        <v>5000</v>
+        <v>24000</v>
       </c>
       <c r="G196" s="6">
-        <v>5000</v>
+        <v>30000</v>
       </c>
       <c r="H196" s="6">
-        <v>5000</v>
+        <v>30000</v>
       </c>
       <c r="I196" s="6">
-        <v>5000</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="197" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A197" s="4" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="B197" s="4" t="s">
-        <v>310</v>
+        <v>245</v>
       </c>
       <c r="C197" s="4"/>
       <c r="D197" s="4"/>
       <c r="E197" s="6">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="F197" s="6">
-        <v>20500</v>
+        <v>600000</v>
       </c>
       <c r="G197" s="6">
-        <v>20000</v>
+        <v>1000000</v>
       </c>
       <c r="H197" s="6">
-        <v>20000</v>
+        <v>600000</v>
       </c>
       <c r="I197" s="6">
-        <v>21000</v>
+        <v>600000</v>
       </c>
     </row>
     <row r="198" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A198" s="4" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="B198" s="4" t="s">
-        <v>311</v>
+        <v>244</v>
       </c>
       <c r="C198" s="4"/>
       <c r="D198" s="4"/>
       <c r="E198" s="6">
-        <v>20000</v>
+        <v>800000</v>
       </c>
       <c r="F198" s="6">
-        <v>22000</v>
+        <v>1000000</v>
       </c>
       <c r="G198" s="6">
-        <v>32000</v>
+        <v>1000000</v>
       </c>
       <c r="H198" s="6">
-        <v>22000</v>
+        <v>600000</v>
       </c>
       <c r="I198" s="6">
-        <v>32000</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="199" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A199" s="4" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="B199" s="4" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="C199" s="4"/>
       <c r="D199" s="4"/>
       <c r="E199" s="6">
-        <v>0</v>
+        <v>400000</v>
       </c>
       <c r="F199" s="6">
-        <v>5000</v>
+        <v>800000</v>
       </c>
       <c r="G199" s="6">
-        <v>5000</v>
+        <v>800000</v>
       </c>
       <c r="H199" s="6">
-        <v>5000</v>
+        <v>800000</v>
       </c>
       <c r="I199" s="6">
-        <v>5000</v>
+        <v>800000</v>
       </c>
     </row>
     <row r="200" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A200" s="4" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="B200" s="4" t="s">
-        <v>504</v>
+        <v>247</v>
       </c>
       <c r="C200" s="4"/>
       <c r="D200" s="4"/>
       <c r="E200" s="6">
-        <v>24000</v>
+        <v>800000</v>
       </c>
       <c r="F200" s="6">
-        <v>24000</v>
+        <v>3000000</v>
       </c>
       <c r="G200" s="6">
-        <v>30000</v>
+        <v>2000000</v>
       </c>
       <c r="H200" s="6">
-        <v>30000</v>
+        <v>2000000</v>
       </c>
       <c r="I200" s="6">
-        <v>30000</v>
+        <v>2000000</v>
       </c>
     </row>
     <row r="201" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A201" s="4" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="B201" s="4" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="C201" s="4"/>
       <c r="D201" s="4"/>
@@ -7394,124 +7392,124 @@
         <v>0</v>
       </c>
       <c r="F201" s="6">
-        <v>600000</v>
+        <v>0</v>
       </c>
       <c r="G201" s="6">
-        <v>1000000</v>
+        <v>50000</v>
       </c>
       <c r="H201" s="6">
-        <v>600000</v>
+        <v>0</v>
       </c>
       <c r="I201" s="6">
-        <v>600000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="202" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A202" s="4" t="s">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="B202" s="4" t="s">
-        <v>244</v>
+        <v>254</v>
       </c>
       <c r="C202" s="4"/>
       <c r="D202" s="4"/>
       <c r="E202" s="6">
-        <v>800000</v>
+        <v>0</v>
       </c>
       <c r="F202" s="6">
-        <v>1000000</v>
+        <v>400000</v>
       </c>
       <c r="G202" s="6">
-        <v>1000000</v>
+        <v>200000</v>
       </c>
       <c r="H202" s="6">
-        <v>600000</v>
+        <v>160000</v>
       </c>
       <c r="I202" s="6">
-        <v>1000000</v>
+        <v>500000</v>
       </c>
     </row>
     <row r="203" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A203" s="4" t="s">
-        <v>246</v>
+        <v>296</v>
       </c>
       <c r="B203" s="4" t="s">
-        <v>248</v>
+        <v>296</v>
       </c>
       <c r="C203" s="4"/>
       <c r="D203" s="4"/>
       <c r="E203" s="6">
-        <v>400000</v>
+        <v>150</v>
       </c>
       <c r="F203" s="6">
-        <v>800000</v>
+        <v>132</v>
       </c>
       <c r="G203" s="6">
-        <v>800000</v>
+        <v>42</v>
       </c>
       <c r="H203" s="6">
-        <v>800000</v>
+        <v>0</v>
       </c>
       <c r="I203" s="6">
-        <v>800000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="204" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A204" s="4" t="s">
-        <v>246</v>
+        <v>467</v>
       </c>
       <c r="B204" s="4" t="s">
-        <v>247</v>
+        <v>467</v>
       </c>
       <c r="C204" s="4"/>
       <c r="D204" s="4"/>
       <c r="E204" s="6">
-        <v>800000</v>
+        <v>0</v>
       </c>
       <c r="F204" s="6">
-        <v>3000000</v>
+        <v>0</v>
       </c>
       <c r="G204" s="6">
-        <v>2000000</v>
+        <v>48</v>
       </c>
       <c r="H204" s="6">
-        <v>2000000</v>
+        <v>0</v>
       </c>
       <c r="I204" s="6">
-        <v>2000000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="205" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A205" s="4" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="B205" s="4" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="C205" s="4"/>
       <c r="D205" s="4"/>
       <c r="E205" s="6">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="F205" s="6">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="G205" s="6">
-        <v>50000</v>
+        <v>500</v>
       </c>
       <c r="H205" s="6">
-        <v>0</v>
+        <v>5500</v>
       </c>
       <c r="I205" s="6">
-        <v>0</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="206" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A206" s="4" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="B206" s="4" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="C206" s="4"/>
       <c r="D206" s="4"/>
@@ -7519,49 +7517,49 @@
         <v>0</v>
       </c>
       <c r="F206" s="6">
-        <v>400000</v>
+        <v>0</v>
       </c>
       <c r="G206" s="6">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="H206" s="6">
-        <v>160000</v>
+        <v>5000</v>
       </c>
       <c r="I206" s="6">
-        <v>500000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="207" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A207" s="4" t="s">
-        <v>296</v>
+        <v>259</v>
       </c>
       <c r="B207" s="4" t="s">
-        <v>296</v>
+        <v>260</v>
       </c>
       <c r="C207" s="4"/>
       <c r="D207" s="4"/>
       <c r="E207" s="6">
-        <v>150</v>
+        <v>8000</v>
       </c>
       <c r="F207" s="6">
-        <v>132</v>
+        <v>18500</v>
       </c>
       <c r="G207" s="6">
-        <v>42</v>
+        <v>21000</v>
       </c>
       <c r="H207" s="6">
-        <v>0</v>
+        <v>23000</v>
       </c>
       <c r="I207" s="6">
-        <v>0</v>
+        <v>23000</v>
       </c>
     </row>
     <row r="208" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A208" s="4" t="s">
-        <v>467</v>
+        <v>261</v>
       </c>
       <c r="B208" s="4" t="s">
-        <v>467</v>
+        <v>262</v>
       </c>
       <c r="C208" s="4"/>
       <c r="D208" s="4"/>
@@ -7569,13 +7567,13 @@
         <v>0</v>
       </c>
       <c r="F208" s="6">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="G208" s="6">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="H208" s="6">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="I208" s="6">
         <v>0</v>
@@ -7583,139 +7581,111 @@
     </row>
     <row r="209" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A209" s="4" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="B209" s="4" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="C209" s="4"/>
       <c r="D209" s="4"/>
       <c r="E209" s="6">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="F209" s="6">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="G209" s="6">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="H209" s="6">
-        <v>5500</v>
+        <v>1000</v>
       </c>
       <c r="I209" s="6">
-        <v>5500</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="210" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A210" s="4" t="s">
-        <v>257</v>
+        <v>298</v>
       </c>
       <c r="B210" s="4" t="s">
-        <v>258</v>
+        <v>298</v>
       </c>
       <c r="C210" s="4"/>
-      <c r="D210" s="4"/>
-      <c r="E210" s="6">
-        <v>0</v>
-      </c>
-      <c r="F210" s="6">
-        <v>0</v>
-      </c>
-      <c r="G210" s="6">
-        <v>0</v>
-      </c>
-      <c r="H210" s="6">
-        <v>5000</v>
-      </c>
-      <c r="I210" s="6">
-        <v>0</v>
-      </c>
+      <c r="D210" s="4">
+        <v>25</v>
+      </c>
+      <c r="E210" s="6"/>
+      <c r="F210" s="6"/>
+      <c r="G210" s="6"/>
+      <c r="H210" s="6"/>
+      <c r="I210" s="6"/>
     </row>
     <row r="211" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A211" s="4" t="s">
-        <v>259</v>
+        <v>601</v>
       </c>
       <c r="B211" s="4" t="s">
-        <v>260</v>
+        <v>602</v>
       </c>
       <c r="C211" s="4"/>
-      <c r="D211" s="4"/>
-      <c r="E211" s="6">
-        <v>8000</v>
-      </c>
-      <c r="F211" s="6">
-        <v>18500</v>
-      </c>
-      <c r="G211" s="6">
-        <v>21000</v>
-      </c>
-      <c r="H211" s="6">
-        <v>23000</v>
-      </c>
-      <c r="I211" s="6">
-        <v>23000</v>
-      </c>
+      <c r="D211" s="4">
+        <v>100000</v>
+      </c>
+      <c r="E211" s="6"/>
+      <c r="F211" s="6"/>
+      <c r="G211" s="6"/>
+      <c r="H211" s="6"/>
+      <c r="I211" s="6"/>
     </row>
     <row r="212" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A212" s="4" t="s">
-        <v>261</v>
+        <v>5</v>
       </c>
       <c r="B212" s="4" t="s">
-        <v>262</v>
+        <v>603</v>
       </c>
       <c r="C212" s="4"/>
-      <c r="D212" s="4"/>
-      <c r="E212" s="6">
-        <v>0</v>
-      </c>
-      <c r="F212" s="6">
-        <v>5000</v>
-      </c>
-      <c r="G212" s="6">
-        <v>0</v>
-      </c>
-      <c r="H212" s="6">
-        <v>5000</v>
-      </c>
-      <c r="I212" s="6">
-        <v>0</v>
-      </c>
+      <c r="D212" s="4">
+        <v>35000</v>
+      </c>
+      <c r="E212" s="6"/>
+      <c r="F212" s="6"/>
+      <c r="G212" s="6"/>
+      <c r="H212" s="6"/>
+      <c r="I212" s="6"/>
     </row>
     <row r="213" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A213" s="4" t="s">
-        <v>263</v>
+        <v>6</v>
       </c>
       <c r="B213" s="4" t="s">
-        <v>264</v>
-      </c>
-      <c r="C213" s="4"/>
-      <c r="D213" s="4"/>
-      <c r="E213" s="6">
-        <v>1000</v>
-      </c>
-      <c r="F213" s="6">
-        <v>1000</v>
-      </c>
-      <c r="G213" s="6">
-        <v>1000</v>
-      </c>
-      <c r="H213" s="6">
-        <v>1000</v>
-      </c>
-      <c r="I213" s="6">
-        <v>1000</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="C213" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D213" s="4">
+        <v>20000</v>
+      </c>
+      <c r="E213" s="6"/>
+      <c r="F213" s="6"/>
+      <c r="G213" s="6"/>
+      <c r="H213" s="6"/>
+      <c r="I213" s="6"/>
     </row>
     <row r="214" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A214" s="4" t="s">
-        <v>298</v>
+        <v>6</v>
       </c>
       <c r="B214" s="4" t="s">
-        <v>298</v>
-      </c>
-      <c r="C214" s="4"/>
+        <v>7</v>
+      </c>
+      <c r="C214" s="4" t="s">
+        <v>9</v>
+      </c>
       <c r="D214" s="4">
-        <v>25</v>
+        <v>50000</v>
       </c>
       <c r="E214" s="6"/>
       <c r="F214" s="6"/>
@@ -7725,14 +7695,14 @@
     </row>
     <row r="215" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A215" s="4" t="s">
-        <v>603</v>
+        <v>6</v>
       </c>
       <c r="B215" s="4" t="s">
-        <v>604</v>
+        <v>7</v>
       </c>
       <c r="C215" s="4"/>
       <c r="D215" s="4">
-        <v>100000</v>
+        <v>300000</v>
       </c>
       <c r="E215" s="6"/>
       <c r="F215" s="6"/>
@@ -7742,14 +7712,14 @@
     </row>
     <row r="216" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A216" s="4" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B216" s="4" t="s">
-        <v>605</v>
+        <v>474</v>
       </c>
       <c r="C216" s="4"/>
       <c r="D216" s="4">
-        <v>35000</v>
+        <v>400000</v>
       </c>
       <c r="E216" s="6"/>
       <c r="F216" s="6"/>
@@ -7759,16 +7729,14 @@
     </row>
     <row r="217" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A217" s="4" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B217" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C217" s="4" t="s">
-        <v>8</v>
-      </c>
+        <v>476</v>
+      </c>
+      <c r="C217" s="4"/>
       <c r="D217" s="4">
-        <v>20000</v>
+        <v>150000</v>
       </c>
       <c r="E217" s="6"/>
       <c r="F217" s="6"/>
@@ -7778,16 +7746,16 @@
     </row>
     <row r="218" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A218" s="4" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B218" s="4" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C218" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D218" s="4">
-        <v>50000</v>
+        <v>100000</v>
       </c>
       <c r="E218" s="6"/>
       <c r="F218" s="6"/>
@@ -7797,14 +7765,14 @@
     </row>
     <row r="219" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A219" s="4" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B219" s="4" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C219" s="4"/>
       <c r="D219" s="4">
-        <v>300000</v>
+        <v>186000</v>
       </c>
       <c r="E219" s="6"/>
       <c r="F219" s="6"/>
@@ -7814,14 +7782,14 @@
     </row>
     <row r="220" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A220" s="4" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B220" s="4" t="s">
-        <v>474</v>
+        <v>604</v>
       </c>
       <c r="C220" s="4"/>
       <c r="D220" s="4">
-        <v>400000</v>
+        <v>380000</v>
       </c>
       <c r="E220" s="6"/>
       <c r="F220" s="6"/>
@@ -7831,14 +7799,14 @@
     </row>
     <row r="221" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A221" s="4" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B221" s="4" t="s">
-        <v>476</v>
+        <v>15</v>
       </c>
       <c r="C221" s="4"/>
       <c r="D221" s="4">
-        <v>150000</v>
+        <v>360000</v>
       </c>
       <c r="E221" s="6"/>
       <c r="F221" s="6"/>
@@ -7848,16 +7816,14 @@
     </row>
     <row r="222" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A222" s="4" t="s">
-        <v>11</v>
+        <v>270</v>
       </c>
       <c r="B222" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C222" s="4" t="s">
-        <v>9</v>
-      </c>
+        <v>605</v>
+      </c>
+      <c r="C222" s="4"/>
       <c r="D222" s="4">
-        <v>100000</v>
+        <v>1000000</v>
       </c>
       <c r="E222" s="6"/>
       <c r="F222" s="6"/>
@@ -7867,14 +7833,14 @@
     </row>
     <row r="223" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A223" s="4" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B223" s="4" t="s">
-        <v>12</v>
+        <v>480</v>
       </c>
       <c r="C223" s="4"/>
       <c r="D223" s="4">
-        <v>186000</v>
+        <v>250000</v>
       </c>
       <c r="E223" s="6"/>
       <c r="F223" s="6"/>
@@ -7884,14 +7850,14 @@
     </row>
     <row r="224" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A224" s="4" t="s">
-        <v>13</v>
+        <v>271</v>
       </c>
       <c r="B224" s="4" t="s">
-        <v>606</v>
+        <v>272</v>
       </c>
       <c r="C224" s="4"/>
       <c r="D224" s="4">
-        <v>380000</v>
+        <v>250000</v>
       </c>
       <c r="E224" s="6"/>
       <c r="F224" s="6"/>
@@ -7901,14 +7867,14 @@
     </row>
     <row r="225" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A225" s="4" t="s">
-        <v>14</v>
+        <v>273</v>
       </c>
       <c r="B225" s="4" t="s">
-        <v>15</v>
+        <v>274</v>
       </c>
       <c r="C225" s="4"/>
       <c r="D225" s="4">
-        <v>360000</v>
+        <v>500000</v>
       </c>
       <c r="E225" s="6"/>
       <c r="F225" s="6"/>
@@ -7918,14 +7884,14 @@
     </row>
     <row r="226" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A226" s="4" t="s">
-        <v>270</v>
+        <v>17</v>
       </c>
       <c r="B226" s="4" t="s">
-        <v>607</v>
+        <v>19</v>
       </c>
       <c r="C226" s="4"/>
       <c r="D226" s="4">
-        <v>1000000</v>
+        <v>2000000</v>
       </c>
       <c r="E226" s="6"/>
       <c r="F226" s="6"/>
@@ -7935,14 +7901,14 @@
     </row>
     <row r="227" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A227" s="4" t="s">
-        <v>16</v>
+        <v>606</v>
       </c>
       <c r="B227" s="4" t="s">
-        <v>480</v>
+        <v>607</v>
       </c>
       <c r="C227" s="4"/>
       <c r="D227" s="4">
-        <v>250000</v>
+        <v>1000000</v>
       </c>
       <c r="E227" s="6"/>
       <c r="F227" s="6"/>
@@ -7952,10 +7918,10 @@
     </row>
     <row r="228" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A228" s="4" t="s">
-        <v>271</v>
+        <v>20</v>
       </c>
       <c r="B228" s="4" t="s">
-        <v>272</v>
+        <v>21</v>
       </c>
       <c r="C228" s="4"/>
       <c r="D228" s="4">
@@ -7969,14 +7935,14 @@
     </row>
     <row r="229" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A229" s="4" t="s">
-        <v>273</v>
+        <v>608</v>
       </c>
       <c r="B229" s="4" t="s">
-        <v>274</v>
+        <v>609</v>
       </c>
       <c r="C229" s="4"/>
       <c r="D229" s="4">
-        <v>500000</v>
+        <v>250000</v>
       </c>
       <c r="E229" s="6"/>
       <c r="F229" s="6"/>
@@ -7986,14 +7952,14 @@
     </row>
     <row r="230" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A230" s="4" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="B230" s="4" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C230" s="4"/>
       <c r="D230" s="4">
-        <v>2000000</v>
+        <v>250000</v>
       </c>
       <c r="E230" s="6"/>
       <c r="F230" s="6"/>
@@ -8003,14 +7969,14 @@
     </row>
     <row r="231" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A231" s="4" t="s">
-        <v>608</v>
+        <v>32</v>
       </c>
       <c r="B231" s="4" t="s">
-        <v>609</v>
+        <v>33</v>
       </c>
       <c r="C231" s="4"/>
       <c r="D231" s="4">
-        <v>1000000</v>
+        <v>30000</v>
       </c>
       <c r="E231" s="6"/>
       <c r="F231" s="6"/>
@@ -8020,14 +7986,14 @@
     </row>
     <row r="232" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A232" s="4" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="B232" s="4" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="C232" s="4"/>
       <c r="D232" s="4">
-        <v>250000</v>
+        <v>120000</v>
       </c>
       <c r="E232" s="6"/>
       <c r="F232" s="6"/>
@@ -8037,14 +8003,14 @@
     </row>
     <row r="233" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A233" s="4" t="s">
-        <v>610</v>
+        <v>38</v>
       </c>
       <c r="B233" s="4" t="s">
-        <v>611</v>
+        <v>39</v>
       </c>
       <c r="C233" s="4"/>
       <c r="D233" s="4">
-        <v>250000</v>
+        <v>400000</v>
       </c>
       <c r="E233" s="6"/>
       <c r="F233" s="6"/>
@@ -8054,14 +8020,14 @@
     </row>
     <row r="234" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A234" s="4" t="s">
-        <v>22</v>
+        <v>299</v>
       </c>
       <c r="B234" s="4" t="s">
-        <v>23</v>
+        <v>300</v>
       </c>
       <c r="C234" s="4"/>
       <c r="D234" s="4">
-        <v>250000</v>
+        <v>70000</v>
       </c>
       <c r="E234" s="6"/>
       <c r="F234" s="6"/>
@@ -8071,14 +8037,14 @@
     </row>
     <row r="235" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A235" s="4" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="B235" s="4" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="C235" s="4"/>
       <c r="D235" s="4">
-        <v>30000</v>
+        <v>120000</v>
       </c>
       <c r="E235" s="6"/>
       <c r="F235" s="6"/>
@@ -8088,14 +8054,14 @@
     </row>
     <row r="236" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A236" s="4" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="B236" s="4" t="s">
-        <v>35</v>
+        <v>482</v>
       </c>
       <c r="C236" s="4"/>
       <c r="D236" s="4">
-        <v>120000</v>
+        <v>150000</v>
       </c>
       <c r="E236" s="6"/>
       <c r="F236" s="6"/>
@@ -8105,14 +8071,14 @@
     </row>
     <row r="237" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A237" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B237" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C237" s="4"/>
       <c r="D237" s="4">
-        <v>400000</v>
+        <v>3000000</v>
       </c>
       <c r="E237" s="6"/>
       <c r="F237" s="6"/>
@@ -8122,14 +8088,14 @@
     </row>
     <row r="238" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A238" s="4" t="s">
-        <v>299</v>
+        <v>40</v>
       </c>
       <c r="B238" s="4" t="s">
-        <v>300</v>
+        <v>43</v>
       </c>
       <c r="C238" s="4"/>
       <c r="D238" s="4">
-        <v>70000</v>
+        <v>1501000</v>
       </c>
       <c r="E238" s="6"/>
       <c r="F238" s="6"/>
@@ -8139,14 +8105,14 @@
     </row>
     <row r="239" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A239" s="4" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B239" s="4" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C239" s="4"/>
       <c r="D239" s="4">
-        <v>120000</v>
+        <v>900000</v>
       </c>
       <c r="E239" s="6"/>
       <c r="F239" s="6"/>
@@ -8156,14 +8122,14 @@
     </row>
     <row r="240" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A240" s="4" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="B240" s="4" t="s">
-        <v>482</v>
+        <v>51</v>
       </c>
       <c r="C240" s="4"/>
       <c r="D240" s="4">
-        <v>150000</v>
+        <v>30000</v>
       </c>
       <c r="E240" s="6"/>
       <c r="F240" s="6"/>
@@ -8173,14 +8139,14 @@
     </row>
     <row r="241" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A241" s="4" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="B241" s="4" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="C241" s="4"/>
       <c r="D241" s="4">
-        <v>3000000</v>
+        <v>50000</v>
       </c>
       <c r="E241" s="6"/>
       <c r="F241" s="6"/>
@@ -8190,14 +8156,14 @@
     </row>
     <row r="242" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A242" s="4" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="B242" s="4" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="C242" s="4"/>
       <c r="D242" s="4">
-        <v>1501000</v>
+        <v>20000</v>
       </c>
       <c r="E242" s="6"/>
       <c r="F242" s="6"/>
@@ -8207,14 +8173,14 @@
     </row>
     <row r="243" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A243" s="4" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="B243" s="4" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="C243" s="4"/>
       <c r="D243" s="4">
-        <v>900000</v>
+        <v>48000</v>
       </c>
       <c r="E243" s="6"/>
       <c r="F243" s="6"/>
@@ -8224,14 +8190,14 @@
     </row>
     <row r="244" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A244" s="4" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="B244" s="4" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="C244" s="4"/>
       <c r="D244" s="4">
-        <v>30000</v>
+        <v>60000</v>
       </c>
       <c r="E244" s="6"/>
       <c r="F244" s="6"/>
@@ -8241,14 +8207,16 @@
     </row>
     <row r="245" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A245" s="4" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="B245" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="C245" s="4"/>
+        <v>610</v>
+      </c>
+      <c r="C245" s="4" t="s">
+        <v>8</v>
+      </c>
       <c r="D245" s="4">
-        <v>50000</v>
+        <v>120000</v>
       </c>
       <c r="E245" s="6"/>
       <c r="F245" s="6"/>
@@ -8258,14 +8226,14 @@
     </row>
     <row r="246" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A246" s="4" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="B246" s="4" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="C246" s="4"/>
       <c r="D246" s="4">
-        <v>20000</v>
+        <v>400000</v>
       </c>
       <c r="E246" s="6"/>
       <c r="F246" s="6"/>
@@ -8275,14 +8243,14 @@
     </row>
     <row r="247" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A247" s="4" t="s">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="B247" s="4" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="C247" s="4"/>
       <c r="D247" s="4">
-        <v>48000</v>
+        <v>30000</v>
       </c>
       <c r="E247" s="6"/>
       <c r="F247" s="6"/>
@@ -8292,14 +8260,14 @@
     </row>
     <row r="248" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A248" s="4" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="B248" s="4" t="s">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="C248" s="4"/>
       <c r="D248" s="4">
-        <v>60000</v>
+        <v>5000</v>
       </c>
       <c r="E248" s="6"/>
       <c r="F248" s="6"/>
@@ -8309,16 +8277,14 @@
     </row>
     <row r="249" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A249" s="4" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="B249" s="4" t="s">
-        <v>612</v>
-      </c>
-      <c r="C249" s="4" t="s">
-        <v>8</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="C249" s="4"/>
       <c r="D249" s="4">
-        <v>120000</v>
+        <v>50000</v>
       </c>
       <c r="E249" s="6"/>
       <c r="F249" s="6"/>
@@ -8328,14 +8294,14 @@
     </row>
     <row r="250" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A250" s="4" t="s">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="B250" s="4" t="s">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="C250" s="4"/>
       <c r="D250" s="4">
-        <v>400000</v>
+        <v>20000</v>
       </c>
       <c r="E250" s="6"/>
       <c r="F250" s="6"/>
@@ -8345,14 +8311,14 @@
     </row>
     <row r="251" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A251" s="4" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="B251" s="4" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="C251" s="4"/>
       <c r="D251" s="4">
-        <v>30000</v>
+        <v>216000</v>
       </c>
       <c r="E251" s="6"/>
       <c r="F251" s="6"/>
@@ -8362,14 +8328,14 @@
     </row>
     <row r="252" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A252" s="4" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="B252" s="4" t="s">
-        <v>73</v>
+        <v>293</v>
       </c>
       <c r="C252" s="4"/>
       <c r="D252" s="4">
-        <v>5000</v>
+        <v>1360000</v>
       </c>
       <c r="E252" s="6"/>
       <c r="F252" s="6"/>
@@ -8379,14 +8345,14 @@
     </row>
     <row r="253" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A253" s="4" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="B253" s="4" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="C253" s="4"/>
       <c r="D253" s="4">
-        <v>50000</v>
+        <v>400000</v>
       </c>
       <c r="E253" s="6"/>
       <c r="F253" s="6"/>
@@ -8396,14 +8362,14 @@
     </row>
     <row r="254" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A254" s="4" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B254" s="4" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="C254" s="4"/>
       <c r="D254" s="4">
-        <v>20000</v>
+        <v>69000</v>
       </c>
       <c r="E254" s="6"/>
       <c r="F254" s="6"/>
@@ -8413,14 +8379,14 @@
     </row>
     <row r="255" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A255" s="4" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="B255" s="4" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="C255" s="4"/>
       <c r="D255" s="4">
-        <v>216000</v>
+        <v>375000</v>
       </c>
       <c r="E255" s="6"/>
       <c r="F255" s="6"/>
@@ -8430,14 +8396,14 @@
     </row>
     <row r="256" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A256" s="4" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="B256" s="4" t="s">
-        <v>293</v>
+        <v>86</v>
       </c>
       <c r="C256" s="4"/>
       <c r="D256" s="4">
-        <v>1360000</v>
+        <v>500000</v>
       </c>
       <c r="E256" s="6"/>
       <c r="F256" s="6"/>
@@ -8447,14 +8413,14 @@
     </row>
     <row r="257" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A257" s="4" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="B257" s="4" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="C257" s="4"/>
       <c r="D257" s="4">
-        <v>400000</v>
+        <v>300000</v>
       </c>
       <c r="E257" s="6"/>
       <c r="F257" s="6"/>
@@ -8464,14 +8430,14 @@
     </row>
     <row r="258" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A258" s="4" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="B258" s="4" t="s">
-        <v>83</v>
+        <v>611</v>
       </c>
       <c r="C258" s="4"/>
       <c r="D258" s="4">
-        <v>69000</v>
+        <v>210000</v>
       </c>
       <c r="E258" s="6"/>
       <c r="F258" s="6"/>
@@ -8481,14 +8447,14 @@
     </row>
     <row r="259" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A259" s="4" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="B259" s="4" t="s">
-        <v>85</v>
+        <v>275</v>
       </c>
       <c r="C259" s="4"/>
       <c r="D259" s="4">
-        <v>375000</v>
+        <v>100000</v>
       </c>
       <c r="E259" s="6"/>
       <c r="F259" s="6"/>
@@ -8498,14 +8464,14 @@
     </row>
     <row r="260" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A260" s="4" t="s">
-        <v>84</v>
+        <v>265</v>
       </c>
       <c r="B260" s="4" t="s">
-        <v>86</v>
+        <v>266</v>
       </c>
       <c r="C260" s="4"/>
       <c r="D260" s="4">
-        <v>500000</v>
+        <v>120000</v>
       </c>
       <c r="E260" s="6"/>
       <c r="F260" s="6"/>
@@ -8515,14 +8481,14 @@
     </row>
     <row r="261" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A261" s="4" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="B261" s="4" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C261" s="4"/>
       <c r="D261" s="4">
-        <v>300000</v>
+        <v>260000</v>
       </c>
       <c r="E261" s="6"/>
       <c r="F261" s="6"/>
@@ -8532,14 +8498,14 @@
     </row>
     <row r="262" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A262" s="4" t="s">
-        <v>89</v>
+        <v>267</v>
       </c>
       <c r="B262" s="4" t="s">
-        <v>613</v>
+        <v>268</v>
       </c>
       <c r="C262" s="4"/>
       <c r="D262" s="4">
-        <v>210000</v>
+        <v>800000</v>
       </c>
       <c r="E262" s="6"/>
       <c r="F262" s="6"/>
@@ -8549,14 +8515,14 @@
     </row>
     <row r="263" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A263" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B263" s="4" t="s">
-        <v>275</v>
+        <v>484</v>
       </c>
       <c r="C263" s="4"/>
       <c r="D263" s="4">
-        <v>100000</v>
+        <v>60000</v>
       </c>
       <c r="E263" s="6"/>
       <c r="F263" s="6"/>
@@ -8566,14 +8532,14 @@
     </row>
     <row r="264" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A264" s="4" t="s">
-        <v>265</v>
+        <v>93</v>
       </c>
       <c r="B264" s="4" t="s">
-        <v>266</v>
+        <v>612</v>
       </c>
       <c r="C264" s="4"/>
       <c r="D264" s="4">
-        <v>120000</v>
+        <v>150000</v>
       </c>
       <c r="E264" s="6"/>
       <c r="F264" s="6"/>
@@ -8583,14 +8549,14 @@
     </row>
     <row r="265" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A265" s="4" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B265" s="4" t="s">
-        <v>90</v>
+        <v>613</v>
       </c>
       <c r="C265" s="4"/>
       <c r="D265" s="4">
-        <v>260000</v>
+        <v>1190000</v>
       </c>
       <c r="E265" s="6"/>
       <c r="F265" s="6"/>
@@ -8600,14 +8566,14 @@
     </row>
     <row r="266" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A266" s="4" t="s">
-        <v>267</v>
+        <v>95</v>
       </c>
       <c r="B266" s="4" t="s">
-        <v>268</v>
+        <v>96</v>
       </c>
       <c r="C266" s="4"/>
       <c r="D266" s="4">
-        <v>800000</v>
+        <v>50000</v>
       </c>
       <c r="E266" s="6"/>
       <c r="F266" s="6"/>
@@ -8617,14 +8583,14 @@
     </row>
     <row r="267" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A267" s="4" t="s">
-        <v>92</v>
+        <v>614</v>
       </c>
       <c r="B267" s="4" t="s">
-        <v>484</v>
+        <v>615</v>
       </c>
       <c r="C267" s="4"/>
       <c r="D267" s="4">
-        <v>60000</v>
+        <v>3000</v>
       </c>
       <c r="E267" s="6"/>
       <c r="F267" s="6"/>
@@ -8634,14 +8600,14 @@
     </row>
     <row r="268" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A268" s="4" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="B268" s="4" t="s">
-        <v>614</v>
+        <v>100</v>
       </c>
       <c r="C268" s="4"/>
       <c r="D268" s="4">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="E268" s="6"/>
       <c r="F268" s="6"/>
@@ -8651,14 +8617,14 @@
     </row>
     <row r="269" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A269" s="4" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="B269" s="4" t="s">
-        <v>615</v>
+        <v>102</v>
       </c>
       <c r="C269" s="4"/>
       <c r="D269" s="4">
-        <v>1190000</v>
+        <v>210000</v>
       </c>
       <c r="E269" s="6"/>
       <c r="F269" s="6"/>
@@ -8668,14 +8634,14 @@
     </row>
     <row r="270" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A270" s="4" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="B270" s="4" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="C270" s="4"/>
       <c r="D270" s="4">
-        <v>50000</v>
+        <v>225000</v>
       </c>
       <c r="E270" s="6"/>
       <c r="F270" s="6"/>
@@ -8685,14 +8651,14 @@
     </row>
     <row r="271" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A271" s="4" t="s">
-        <v>616</v>
+        <v>109</v>
       </c>
       <c r="B271" s="4" t="s">
-        <v>617</v>
+        <v>110</v>
       </c>
       <c r="C271" s="4"/>
       <c r="D271" s="4">
-        <v>3000</v>
+        <v>100000</v>
       </c>
       <c r="E271" s="6"/>
       <c r="F271" s="6"/>
@@ -8702,14 +8668,14 @@
     </row>
     <row r="272" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A272" s="4" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="B272" s="4" t="s">
-        <v>100</v>
+        <v>616</v>
       </c>
       <c r="C272" s="4"/>
       <c r="D272" s="4">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="E272" s="6"/>
       <c r="F272" s="6"/>
@@ -8719,14 +8685,14 @@
     </row>
     <row r="273" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A273" s="4" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="B273" s="4" t="s">
-        <v>102</v>
+        <v>486</v>
       </c>
       <c r="C273" s="4"/>
       <c r="D273" s="4">
-        <v>210000</v>
+        <v>800000</v>
       </c>
       <c r="E273" s="6"/>
       <c r="F273" s="6"/>
@@ -8736,14 +8702,14 @@
     </row>
     <row r="274" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A274" s="4" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="B274" s="4" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="C274" s="4"/>
       <c r="D274" s="4">
-        <v>225000</v>
+        <v>1242000</v>
       </c>
       <c r="E274" s="6"/>
       <c r="F274" s="6"/>
@@ -8753,14 +8719,14 @@
     </row>
     <row r="275" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A275" s="4" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="B275" s="4" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="C275" s="4"/>
       <c r="D275" s="4">
-        <v>100000</v>
+        <v>70000</v>
       </c>
       <c r="E275" s="6"/>
       <c r="F275" s="6"/>
@@ -8770,14 +8736,14 @@
     </row>
     <row r="276" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A276" s="4" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="B276" s="4" t="s">
-        <v>618</v>
+        <v>276</v>
       </c>
       <c r="C276" s="4"/>
       <c r="D276" s="4">
-        <v>200000</v>
+        <v>70000</v>
       </c>
       <c r="E276" s="6"/>
       <c r="F276" s="6"/>
@@ -8787,14 +8753,14 @@
     </row>
     <row r="277" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A277" s="4" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="B277" s="4" t="s">
-        <v>486</v>
+        <v>120</v>
       </c>
       <c r="C277" s="4"/>
       <c r="D277" s="4">
-        <v>800000</v>
+        <v>55000</v>
       </c>
       <c r="E277" s="6"/>
       <c r="F277" s="6"/>
@@ -8804,14 +8770,14 @@
     </row>
     <row r="278" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A278" s="4" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="B278" s="4" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="C278" s="4"/>
       <c r="D278" s="4">
-        <v>1242000</v>
+        <v>5000</v>
       </c>
       <c r="E278" s="6"/>
       <c r="F278" s="6"/>
@@ -8821,14 +8787,14 @@
     </row>
     <row r="279" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A279" s="4" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="B279" s="4" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="C279" s="4"/>
       <c r="D279" s="4">
-        <v>70000</v>
+        <v>30000</v>
       </c>
       <c r="E279" s="6"/>
       <c r="F279" s="6"/>
@@ -8838,14 +8804,14 @@
     </row>
     <row r="280" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A280" s="4" t="s">
-        <v>116</v>
+        <v>305</v>
       </c>
       <c r="B280" s="4" t="s">
-        <v>276</v>
+        <v>306</v>
       </c>
       <c r="C280" s="4"/>
       <c r="D280" s="4">
-        <v>70000</v>
+        <v>20000</v>
       </c>
       <c r="E280" s="6"/>
       <c r="F280" s="6"/>
@@ -8855,14 +8821,14 @@
     </row>
     <row r="281" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A281" s="4" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="B281" s="4" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="C281" s="4"/>
       <c r="D281" s="4">
-        <v>55000</v>
+        <v>105000</v>
       </c>
       <c r="E281" s="6"/>
       <c r="F281" s="6"/>
@@ -8872,14 +8838,14 @@
     </row>
     <row r="282" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A282" s="4" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="B282" s="4" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="C282" s="4"/>
       <c r="D282" s="4">
-        <v>5000</v>
+        <v>105000</v>
       </c>
       <c r="E282" s="6"/>
       <c r="F282" s="6"/>
@@ -8889,14 +8855,16 @@
     </row>
     <row r="283" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A283" s="4" t="s">
-        <v>126</v>
+        <v>494</v>
       </c>
       <c r="B283" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="C283" s="4"/>
+        <v>493</v>
+      </c>
+      <c r="C283" s="4" t="s">
+        <v>617</v>
+      </c>
       <c r="D283" s="4">
-        <v>30000</v>
+        <v>2000000</v>
       </c>
       <c r="E283" s="6"/>
       <c r="F283" s="6"/>
@@ -8906,14 +8874,14 @@
     </row>
     <row r="284" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A284" s="4" t="s">
-        <v>305</v>
+        <v>133</v>
       </c>
       <c r="B284" s="4" t="s">
-        <v>306</v>
+        <v>134</v>
       </c>
       <c r="C284" s="4"/>
       <c r="D284" s="4">
-        <v>20000</v>
+        <v>2000</v>
       </c>
       <c r="E284" s="6"/>
       <c r="F284" s="6"/>
@@ -8923,14 +8891,14 @@
     </row>
     <row r="285" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A285" s="4" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="B285" s="4" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="C285" s="4"/>
       <c r="D285" s="4">
-        <v>105000</v>
+        <v>750000</v>
       </c>
       <c r="E285" s="6"/>
       <c r="F285" s="6"/>
@@ -8940,14 +8908,14 @@
     </row>
     <row r="286" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A286" s="4" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="B286" s="4" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="C286" s="4"/>
       <c r="D286" s="4">
-        <v>105000</v>
+        <v>20000</v>
       </c>
       <c r="E286" s="6"/>
       <c r="F286" s="6"/>
@@ -8957,16 +8925,14 @@
     </row>
     <row r="287" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A287" s="4" t="s">
-        <v>494</v>
+        <v>141</v>
       </c>
       <c r="B287" s="4" t="s">
-        <v>493</v>
-      </c>
-      <c r="C287" s="4" t="s">
-        <v>619</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="C287" s="4"/>
       <c r="D287" s="4">
-        <v>2000000</v>
+        <v>30000</v>
       </c>
       <c r="E287" s="6"/>
       <c r="F287" s="6"/>
@@ -8976,14 +8942,14 @@
     </row>
     <row r="288" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A288" s="4" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="B288" s="4" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="C288" s="4"/>
       <c r="D288" s="4">
-        <v>2000</v>
+        <v>2055000</v>
       </c>
       <c r="E288" s="6"/>
       <c r="F288" s="6"/>
@@ -8993,14 +8959,14 @@
     </row>
     <row r="289" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A289" s="4" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="B289" s="4" t="s">
-        <v>136</v>
+        <v>150</v>
       </c>
       <c r="C289" s="4"/>
       <c r="D289" s="4">
-        <v>750000</v>
+        <v>2055000</v>
       </c>
       <c r="E289" s="6"/>
       <c r="F289" s="6"/>
@@ -9010,14 +8976,14 @@
     </row>
     <row r="290" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A290" s="4" t="s">
-        <v>139</v>
+        <v>153</v>
       </c>
       <c r="B290" s="4" t="s">
-        <v>140</v>
+        <v>154</v>
       </c>
       <c r="C290" s="4"/>
       <c r="D290" s="4">
-        <v>20000</v>
+        <v>123000</v>
       </c>
       <c r="E290" s="6"/>
       <c r="F290" s="6"/>
@@ -9027,14 +8993,14 @@
     </row>
     <row r="291" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A291" s="4" t="s">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="B291" s="4" t="s">
-        <v>142</v>
+        <v>156</v>
       </c>
       <c r="C291" s="4"/>
       <c r="D291" s="4">
-        <v>30000</v>
+        <v>3000</v>
       </c>
       <c r="E291" s="6"/>
       <c r="F291" s="6"/>
@@ -9044,14 +9010,14 @@
     </row>
     <row r="292" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A292" s="4" t="s">
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="B292" s="4" t="s">
-        <v>146</v>
+        <v>159</v>
       </c>
       <c r="C292" s="4"/>
       <c r="D292" s="4">
-        <v>2055000</v>
+        <v>500000</v>
       </c>
       <c r="E292" s="6"/>
       <c r="F292" s="6"/>
@@ -9061,14 +9027,14 @@
     </row>
     <row r="293" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A293" s="4" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="B293" s="4" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="C293" s="4"/>
       <c r="D293" s="4">
-        <v>2055000</v>
+        <v>2000</v>
       </c>
       <c r="E293" s="6"/>
       <c r="F293" s="6"/>
@@ -9078,14 +9044,14 @@
     </row>
     <row r="294" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A294" s="4" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="B294" s="4" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="C294" s="4"/>
       <c r="D294" s="4">
-        <v>123000</v>
+        <v>30000</v>
       </c>
       <c r="E294" s="6"/>
       <c r="F294" s="6"/>
@@ -9095,14 +9061,14 @@
     </row>
     <row r="295" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A295" s="4" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="B295" s="4" t="s">
-        <v>156</v>
+        <v>618</v>
       </c>
       <c r="C295" s="4"/>
       <c r="D295" s="4">
-        <v>3000</v>
+        <v>100000</v>
       </c>
       <c r="E295" s="6"/>
       <c r="F295" s="6"/>
@@ -9112,14 +9078,14 @@
     </row>
     <row r="296" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A296" s="4" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="B296" s="4" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="C296" s="4"/>
       <c r="D296" s="4">
-        <v>500000</v>
+        <v>180000</v>
       </c>
       <c r="E296" s="6"/>
       <c r="F296" s="6"/>
@@ -9129,14 +9095,14 @@
     </row>
     <row r="297" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A297" s="4" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="B297" s="4" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="C297" s="4"/>
       <c r="D297" s="4">
-        <v>2000</v>
+        <v>80000</v>
       </c>
       <c r="E297" s="6"/>
       <c r="F297" s="6"/>
@@ -9146,14 +9112,14 @@
     </row>
     <row r="298" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A298" s="4" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="B298" s="4" t="s">
-        <v>161</v>
+        <v>619</v>
       </c>
       <c r="C298" s="4"/>
       <c r="D298" s="4">
-        <v>30000</v>
+        <v>50000</v>
       </c>
       <c r="E298" s="6"/>
       <c r="F298" s="6"/>
@@ -9163,14 +9129,14 @@
     </row>
     <row r="299" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A299" s="4" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="B299" s="4" t="s">
         <v>620</v>
       </c>
       <c r="C299" s="4"/>
       <c r="D299" s="4">
-        <v>100000</v>
+        <v>5000</v>
       </c>
       <c r="E299" s="6"/>
       <c r="F299" s="6"/>
@@ -9180,14 +9146,14 @@
     </row>
     <row r="300" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A300" s="4" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="B300" s="4" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="C300" s="4"/>
       <c r="D300" s="4">
-        <v>180000</v>
+        <v>2000</v>
       </c>
       <c r="E300" s="6"/>
       <c r="F300" s="6"/>
@@ -9197,14 +9163,14 @@
     </row>
     <row r="301" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A301" s="4" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="B301" s="4" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="C301" s="4"/>
       <c r="D301" s="4">
-        <v>80000</v>
+        <v>200000</v>
       </c>
       <c r="E301" s="6"/>
       <c r="F301" s="6"/>
@@ -9214,14 +9180,14 @@
     </row>
     <row r="302" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A302" s="4" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="B302" s="4" t="s">
-        <v>621</v>
+        <v>496</v>
       </c>
       <c r="C302" s="4"/>
       <c r="D302" s="4">
-        <v>50000</v>
+        <v>1000</v>
       </c>
       <c r="E302" s="6"/>
       <c r="F302" s="6"/>
@@ -9231,14 +9197,14 @@
     </row>
     <row r="303" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A303" s="4" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="B303" s="4" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="C303" s="4"/>
       <c r="D303" s="4">
-        <v>5000</v>
+        <v>30000</v>
       </c>
       <c r="E303" s="6"/>
       <c r="F303" s="6"/>
@@ -9248,14 +9214,14 @@
     </row>
     <row r="304" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A304" s="4" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="B304" s="4" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="C304" s="4"/>
       <c r="D304" s="4">
-        <v>2000</v>
+        <v>50000</v>
       </c>
       <c r="E304" s="6"/>
       <c r="F304" s="6"/>
@@ -9265,14 +9231,14 @@
     </row>
     <row r="305" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A305" s="4" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="B305" s="4" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="C305" s="4"/>
       <c r="D305" s="4">
-        <v>200000</v>
+        <v>100000</v>
       </c>
       <c r="E305" s="6"/>
       <c r="F305" s="6"/>
@@ -9282,14 +9248,14 @@
     </row>
     <row r="306" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A306" s="4" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="B306" s="4" t="s">
-        <v>496</v>
+        <v>279</v>
       </c>
       <c r="C306" s="4"/>
       <c r="D306" s="4">
-        <v>1000</v>
+        <v>124000</v>
       </c>
       <c r="E306" s="6"/>
       <c r="F306" s="6"/>
@@ -9299,14 +9265,14 @@
     </row>
     <row r="307" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A307" s="4" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="B307" s="4" t="s">
-        <v>623</v>
+        <v>181</v>
       </c>
       <c r="C307" s="4"/>
       <c r="D307" s="4">
-        <v>30000</v>
+        <v>700000</v>
       </c>
       <c r="E307" s="6"/>
       <c r="F307" s="6"/>
@@ -9316,14 +9282,14 @@
     </row>
     <row r="308" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A308" s="4" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="B308" s="4" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="C308" s="4"/>
       <c r="D308" s="4">
-        <v>50000</v>
+        <v>102000</v>
       </c>
       <c r="E308" s="6"/>
       <c r="F308" s="6"/>
@@ -9333,14 +9299,14 @@
     </row>
     <row r="309" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A309" s="4" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="B309" s="4" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="C309" s="4"/>
       <c r="D309" s="4">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="E309" s="6"/>
       <c r="F309" s="6"/>
@@ -9350,14 +9316,14 @@
     </row>
     <row r="310" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A310" s="4" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="B310" s="4" t="s">
-        <v>279</v>
+        <v>185</v>
       </c>
       <c r="C310" s="4"/>
       <c r="D310" s="4">
-        <v>124000</v>
+        <v>501000</v>
       </c>
       <c r="E310" s="6"/>
       <c r="F310" s="6"/>
@@ -9367,14 +9333,14 @@
     </row>
     <row r="311" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A311" s="4" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="B311" s="4" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="C311" s="4"/>
       <c r="D311" s="4">
-        <v>700000</v>
+        <v>2000000</v>
       </c>
       <c r="E311" s="6"/>
       <c r="F311" s="6"/>
@@ -9384,14 +9350,14 @@
     </row>
     <row r="312" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A312" s="4" t="s">
-        <v>179</v>
+        <v>622</v>
       </c>
       <c r="B312" s="4" t="s">
-        <v>180</v>
+        <v>623</v>
       </c>
       <c r="C312" s="4"/>
       <c r="D312" s="4">
-        <v>102000</v>
+        <v>40000</v>
       </c>
       <c r="E312" s="6"/>
       <c r="F312" s="6"/>
@@ -9401,14 +9367,14 @@
     </row>
     <row r="313" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A313" s="4" t="s">
-        <v>182</v>
+        <v>308</v>
       </c>
       <c r="B313" s="4" t="s">
-        <v>183</v>
+        <v>307</v>
       </c>
       <c r="C313" s="4"/>
       <c r="D313" s="4">
-        <v>200000</v>
+        <v>60000</v>
       </c>
       <c r="E313" s="6"/>
       <c r="F313" s="6"/>
@@ -9418,14 +9384,14 @@
     </row>
     <row r="314" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A314" s="4" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="B314" s="4" t="s">
-        <v>185</v>
+        <v>280</v>
       </c>
       <c r="C314" s="4"/>
       <c r="D314" s="4">
-        <v>501000</v>
+        <v>30000</v>
       </c>
       <c r="E314" s="6"/>
       <c r="F314" s="6"/>
@@ -9435,14 +9401,14 @@
     </row>
     <row r="315" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A315" s="4" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="B315" s="4" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="C315" s="4"/>
       <c r="D315" s="4">
-        <v>2000000</v>
+        <v>30000</v>
       </c>
       <c r="E315" s="6"/>
       <c r="F315" s="6"/>
@@ -9452,14 +9418,14 @@
     </row>
     <row r="316" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A316" s="4" t="s">
-        <v>624</v>
+        <v>195</v>
       </c>
       <c r="B316" s="4" t="s">
-        <v>625</v>
+        <v>196</v>
       </c>
       <c r="C316" s="4"/>
       <c r="D316" s="4">
-        <v>40000</v>
+        <v>4000</v>
       </c>
       <c r="E316" s="6"/>
       <c r="F316" s="6"/>
@@ -9469,14 +9435,14 @@
     </row>
     <row r="317" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A317" s="4" t="s">
-        <v>308</v>
+        <v>197</v>
       </c>
       <c r="B317" s="4" t="s">
-        <v>307</v>
+        <v>198</v>
       </c>
       <c r="C317" s="4"/>
       <c r="D317" s="4">
-        <v>60000</v>
+        <v>11000</v>
       </c>
       <c r="E317" s="6"/>
       <c r="F317" s="6"/>
@@ -9486,14 +9452,14 @@
     </row>
     <row r="318" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A318" s="4" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="B318" s="4" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C318" s="4"/>
       <c r="D318" s="4">
-        <v>30000</v>
+        <v>20000</v>
       </c>
       <c r="E318" s="6"/>
       <c r="F318" s="6"/>
@@ -9503,14 +9469,14 @@
     </row>
     <row r="319" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A319" s="4" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="B319" s="4" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="C319" s="4"/>
       <c r="D319" s="4">
-        <v>30000</v>
+        <v>3000</v>
       </c>
       <c r="E319" s="6"/>
       <c r="F319" s="6"/>
@@ -9520,14 +9486,14 @@
     </row>
     <row r="320" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A320" s="4" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="B320" s="4" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="C320" s="4"/>
       <c r="D320" s="4">
-        <v>4000</v>
+        <v>116000</v>
       </c>
       <c r="E320" s="6"/>
       <c r="F320" s="6"/>
@@ -9537,14 +9503,14 @@
     </row>
     <row r="321" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A321" s="4" t="s">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="B321" s="4" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="C321" s="4"/>
       <c r="D321" s="4">
-        <v>11000</v>
+        <v>87000</v>
       </c>
       <c r="E321" s="6"/>
       <c r="F321" s="6"/>
@@ -9554,14 +9520,14 @@
     </row>
     <row r="322" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A322" s="4" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="B322" s="4" t="s">
-        <v>281</v>
+        <v>207</v>
       </c>
       <c r="C322" s="4"/>
       <c r="D322" s="4">
-        <v>20000</v>
+        <v>100000</v>
       </c>
       <c r="E322" s="6"/>
       <c r="F322" s="6"/>
@@ -9571,14 +9537,14 @@
     </row>
     <row r="323" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A323" s="4" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="B323" s="4" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="C323" s="4"/>
       <c r="D323" s="4">
-        <v>3000</v>
+        <v>50000</v>
       </c>
       <c r="E323" s="6"/>
       <c r="F323" s="6"/>
@@ -9588,14 +9554,14 @@
     </row>
     <row r="324" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A324" s="4" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="B324" s="4" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="C324" s="4"/>
       <c r="D324" s="4">
-        <v>116000</v>
+        <v>4000</v>
       </c>
       <c r="E324" s="6"/>
       <c r="F324" s="6"/>
@@ -9605,14 +9571,14 @@
     </row>
     <row r="325" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A325" s="4" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="B325" s="4" t="s">
-        <v>209</v>
+        <v>499</v>
       </c>
       <c r="C325" s="4"/>
       <c r="D325" s="4">
-        <v>87000</v>
+        <v>16000</v>
       </c>
       <c r="E325" s="6"/>
       <c r="F325" s="6"/>
@@ -9622,14 +9588,14 @@
     </row>
     <row r="326" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A326" s="4" t="s">
-        <v>206</v>
+        <v>624</v>
       </c>
       <c r="B326" s="4" t="s">
-        <v>207</v>
+        <v>625</v>
       </c>
       <c r="C326" s="4"/>
       <c r="D326" s="4">
-        <v>100000</v>
+        <v>5000</v>
       </c>
       <c r="E326" s="6"/>
       <c r="F326" s="6"/>
@@ -9639,14 +9605,14 @@
     </row>
     <row r="327" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A327" s="4" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="B327" s="4" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="C327" s="4"/>
       <c r="D327" s="4">
-        <v>50000</v>
+        <v>219000</v>
       </c>
       <c r="E327" s="6"/>
       <c r="F327" s="6"/>
@@ -9656,14 +9622,14 @@
     </row>
     <row r="328" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A328" s="4" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="B328" s="4" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="C328" s="4"/>
       <c r="D328" s="4">
-        <v>4000</v>
+        <v>90000</v>
       </c>
       <c r="E328" s="6"/>
       <c r="F328" s="6"/>
@@ -9673,14 +9639,14 @@
     </row>
     <row r="329" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A329" s="4" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B329" s="4" t="s">
-        <v>499</v>
+        <v>218</v>
       </c>
       <c r="C329" s="4"/>
       <c r="D329" s="4">
-        <v>16000</v>
+        <v>20000</v>
       </c>
       <c r="E329" s="6"/>
       <c r="F329" s="6"/>
@@ -9690,14 +9656,14 @@
     </row>
     <row r="330" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A330" s="4" t="s">
-        <v>626</v>
+        <v>219</v>
       </c>
       <c r="B330" s="4" t="s">
-        <v>627</v>
+        <v>220</v>
       </c>
       <c r="C330" s="4"/>
       <c r="D330" s="4">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="E330" s="6"/>
       <c r="F330" s="6"/>
@@ -9707,14 +9673,14 @@
     </row>
     <row r="331" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A331" s="4" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="B331" s="4" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="C331" s="4"/>
       <c r="D331" s="4">
-        <v>219000</v>
+        <v>1000</v>
       </c>
       <c r="E331" s="6"/>
       <c r="F331" s="6"/>
@@ -9724,14 +9690,14 @@
     </row>
     <row r="332" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A332" s="4" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="B332" s="4" t="s">
-        <v>216</v>
+        <v>284</v>
       </c>
       <c r="C332" s="4"/>
       <c r="D332" s="4">
-        <v>90000</v>
+        <v>50000</v>
       </c>
       <c r="E332" s="6"/>
       <c r="F332" s="6"/>
@@ -9741,14 +9707,14 @@
     </row>
     <row r="333" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A333" s="4" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="B333" s="4" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="C333" s="4"/>
       <c r="D333" s="4">
-        <v>20000</v>
+        <v>350000</v>
       </c>
       <c r="E333" s="6"/>
       <c r="F333" s="6"/>
@@ -9758,14 +9724,14 @@
     </row>
     <row r="334" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A334" s="4" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="B334" s="4" t="s">
-        <v>220</v>
+        <v>285</v>
       </c>
       <c r="C334" s="4"/>
       <c r="D334" s="4">
-        <v>10000</v>
+        <v>105000</v>
       </c>
       <c r="E334" s="6"/>
       <c r="F334" s="6"/>
@@ -9775,14 +9741,14 @@
     </row>
     <row r="335" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A335" s="4" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="B335" s="4" t="s">
-        <v>222</v>
+        <v>286</v>
       </c>
       <c r="C335" s="4"/>
       <c r="D335" s="4">
-        <v>1000</v>
+        <v>150000</v>
       </c>
       <c r="E335" s="6"/>
       <c r="F335" s="6"/>
@@ -9792,14 +9758,14 @@
     </row>
     <row r="336" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A336" s="4" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="B336" s="4" t="s">
-        <v>284</v>
+        <v>227</v>
       </c>
       <c r="C336" s="4"/>
       <c r="D336" s="4">
-        <v>50000</v>
+        <v>450000</v>
       </c>
       <c r="E336" s="6"/>
       <c r="F336" s="6"/>
@@ -9809,14 +9775,14 @@
     </row>
     <row r="337" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A337" s="4" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B337" s="4" t="s">
-        <v>224</v>
+        <v>287</v>
       </c>
       <c r="C337" s="4"/>
       <c r="D337" s="4">
-        <v>350000</v>
+        <v>175000</v>
       </c>
       <c r="E337" s="6"/>
       <c r="F337" s="6"/>
@@ -9826,14 +9792,14 @@
     </row>
     <row r="338" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A338" s="4" t="s">
-        <v>225</v>
+        <v>626</v>
       </c>
       <c r="B338" s="4" t="s">
-        <v>285</v>
+        <v>627</v>
       </c>
       <c r="C338" s="4"/>
       <c r="D338" s="4">
-        <v>105000</v>
+        <v>3000</v>
       </c>
       <c r="E338" s="6"/>
       <c r="F338" s="6"/>
@@ -9843,10 +9809,10 @@
     </row>
     <row r="339" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A339" s="4" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B339" s="4" t="s">
-        <v>286</v>
+        <v>229</v>
       </c>
       <c r="C339" s="4"/>
       <c r="D339" s="4">
@@ -9860,14 +9826,14 @@
     </row>
     <row r="340" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A340" s="4" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B340" s="4" t="s">
-        <v>227</v>
+        <v>288</v>
       </c>
       <c r="C340" s="4"/>
       <c r="D340" s="4">
-        <v>450000</v>
+        <v>336000</v>
       </c>
       <c r="E340" s="6"/>
       <c r="F340" s="6"/>
@@ -9877,14 +9843,14 @@
     </row>
     <row r="341" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A341" s="4" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="B341" s="4" t="s">
-        <v>287</v>
+        <v>231</v>
       </c>
       <c r="C341" s="4"/>
       <c r="D341" s="4">
-        <v>175000</v>
+        <v>245000</v>
       </c>
       <c r="E341" s="6"/>
       <c r="F341" s="6"/>
@@ -9894,14 +9860,14 @@
     </row>
     <row r="342" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A342" s="4" t="s">
-        <v>628</v>
+        <v>230</v>
       </c>
       <c r="B342" s="4" t="s">
-        <v>629</v>
+        <v>290</v>
       </c>
       <c r="C342" s="4"/>
       <c r="D342" s="4">
-        <v>3000</v>
+        <v>6000</v>
       </c>
       <c r="E342" s="6"/>
       <c r="F342" s="6"/>
@@ -9911,14 +9877,14 @@
     </row>
     <row r="343" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A343" s="4" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="B343" s="4" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="C343" s="4"/>
       <c r="D343" s="4">
-        <v>150000</v>
+        <v>165000</v>
       </c>
       <c r="E343" s="6"/>
       <c r="F343" s="6"/>
@@ -9928,14 +9894,14 @@
     </row>
     <row r="344" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A344" s="4" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="B344" s="4" t="s">
-        <v>288</v>
+        <v>234</v>
       </c>
       <c r="C344" s="4"/>
       <c r="D344" s="4">
-        <v>336000</v>
+        <v>120000</v>
       </c>
       <c r="E344" s="6"/>
       <c r="F344" s="6"/>
@@ -9945,14 +9911,14 @@
     </row>
     <row r="345" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A345" s="4" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="B345" s="4" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="C345" s="4"/>
       <c r="D345" s="4">
-        <v>245000</v>
+        <v>396000</v>
       </c>
       <c r="E345" s="6"/>
       <c r="F345" s="6"/>
@@ -9962,14 +9928,14 @@
     </row>
     <row r="346" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A346" s="4" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="B346" s="4" t="s">
-        <v>290</v>
+        <v>309</v>
       </c>
       <c r="C346" s="4"/>
       <c r="D346" s="4">
-        <v>6000</v>
+        <v>5000</v>
       </c>
       <c r="E346" s="6"/>
       <c r="F346" s="6"/>
@@ -9979,14 +9945,14 @@
     </row>
     <row r="347" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A347" s="4" t="s">
-        <v>233</v>
+        <v>628</v>
       </c>
       <c r="B347" s="4" t="s">
-        <v>232</v>
+        <v>629</v>
       </c>
       <c r="C347" s="4"/>
       <c r="D347" s="4">
-        <v>165000</v>
+        <v>3200</v>
       </c>
       <c r="E347" s="6"/>
       <c r="F347" s="6"/>
@@ -9996,14 +9962,14 @@
     </row>
     <row r="348" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A348" s="4" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="B348" s="4" t="s">
-        <v>234</v>
+        <v>310</v>
       </c>
       <c r="C348" s="4"/>
       <c r="D348" s="4">
-        <v>120000</v>
+        <v>10000</v>
       </c>
       <c r="E348" s="6"/>
       <c r="F348" s="6"/>
@@ -10013,14 +9979,14 @@
     </row>
     <row r="349" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A349" s="4" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="B349" s="4" t="s">
-        <v>236</v>
+        <v>311</v>
       </c>
       <c r="C349" s="4"/>
       <c r="D349" s="4">
-        <v>396000</v>
+        <v>12000</v>
       </c>
       <c r="E349" s="6"/>
       <c r="F349" s="6"/>
@@ -10030,14 +9996,14 @@
     </row>
     <row r="350" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A350" s="4" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="B350" s="4" t="s">
-        <v>309</v>
+        <v>241</v>
       </c>
       <c r="C350" s="4"/>
       <c r="D350" s="4">
-        <v>5000</v>
+        <v>12000</v>
       </c>
       <c r="E350" s="6"/>
       <c r="F350" s="6"/>
@@ -10047,14 +10013,14 @@
     </row>
     <row r="351" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A351" s="4" t="s">
-        <v>630</v>
+        <v>242</v>
       </c>
       <c r="B351" s="4" t="s">
-        <v>631</v>
+        <v>504</v>
       </c>
       <c r="C351" s="4"/>
       <c r="D351" s="4">
-        <v>3200</v>
+        <v>41000</v>
       </c>
       <c r="E351" s="6"/>
       <c r="F351" s="6"/>
@@ -10064,14 +10030,14 @@
     </row>
     <row r="352" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A352" s="4" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="B352" s="4" t="s">
-        <v>310</v>
+        <v>248</v>
       </c>
       <c r="C352" s="4"/>
       <c r="D352" s="4">
-        <v>10000</v>
+        <v>800000</v>
       </c>
       <c r="E352" s="6"/>
       <c r="F352" s="6"/>
@@ -10081,14 +10047,14 @@
     </row>
     <row r="353" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A353" s="4" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="B353" s="4" t="s">
-        <v>311</v>
+        <v>247</v>
       </c>
       <c r="C353" s="4"/>
       <c r="D353" s="4">
-        <v>12000</v>
+        <v>1200000</v>
       </c>
       <c r="E353" s="6"/>
       <c r="F353" s="6"/>
@@ -10098,14 +10064,16 @@
     </row>
     <row r="354" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A354" s="4" t="s">
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="B354" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="C354" s="4"/>
+        <v>250</v>
+      </c>
+      <c r="C354" s="4" t="s">
+        <v>630</v>
+      </c>
       <c r="D354" s="4">
-        <v>12000</v>
+        <v>100000</v>
       </c>
       <c r="E354" s="6"/>
       <c r="F354" s="6"/>
@@ -10115,14 +10083,14 @@
     </row>
     <row r="355" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A355" s="4" t="s">
-        <v>242</v>
+        <v>251</v>
       </c>
       <c r="B355" s="4" t="s">
-        <v>504</v>
+        <v>252</v>
       </c>
       <c r="C355" s="4"/>
       <c r="D355" s="4">
-        <v>41000</v>
+        <v>192000</v>
       </c>
       <c r="E355" s="6"/>
       <c r="F355" s="6"/>
@@ -10132,14 +10100,14 @@
     </row>
     <row r="356" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A356" s="4" t="s">
-        <v>246</v>
+        <v>296</v>
       </c>
       <c r="B356" s="4" t="s">
-        <v>248</v>
+        <v>296</v>
       </c>
       <c r="C356" s="4"/>
       <c r="D356" s="4">
-        <v>800000</v>
+        <v>200</v>
       </c>
       <c r="E356" s="6"/>
       <c r="F356" s="6"/>
@@ -10149,14 +10117,14 @@
     </row>
     <row r="357" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A357" s="4" t="s">
-        <v>246</v>
+        <v>467</v>
       </c>
       <c r="B357" s="4" t="s">
-        <v>247</v>
+        <v>467</v>
       </c>
       <c r="C357" s="4"/>
       <c r="D357" s="4">
-        <v>1200000</v>
+        <v>40</v>
       </c>
       <c r="E357" s="6"/>
       <c r="F357" s="6"/>
@@ -10166,16 +10134,14 @@
     </row>
     <row r="358" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A358" s="4" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="B358" s="4" t="s">
-        <v>250</v>
-      </c>
-      <c r="C358" s="4" t="s">
-        <v>632</v>
-      </c>
+        <v>631</v>
+      </c>
+      <c r="C358" s="4"/>
       <c r="D358" s="4">
-        <v>100000</v>
+        <v>4000</v>
       </c>
       <c r="E358" s="6"/>
       <c r="F358" s="6"/>
@@ -10185,14 +10151,14 @@
     </row>
     <row r="359" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A359" s="4" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="B359" s="4" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="C359" s="4"/>
       <c r="D359" s="4">
-        <v>192000</v>
+        <v>500</v>
       </c>
       <c r="E359" s="6"/>
       <c r="F359" s="6"/>
@@ -10202,14 +10168,14 @@
     </row>
     <row r="360" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A360" s="4" t="s">
-        <v>296</v>
+        <v>632</v>
       </c>
       <c r="B360" s="4" t="s">
-        <v>296</v>
+        <v>633</v>
       </c>
       <c r="C360" s="4"/>
       <c r="D360" s="4">
-        <v>200</v>
+        <v>5000</v>
       </c>
       <c r="E360" s="6"/>
       <c r="F360" s="6"/>
@@ -10219,14 +10185,14 @@
     </row>
     <row r="361" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A361" s="4" t="s">
-        <v>467</v>
+        <v>259</v>
       </c>
       <c r="B361" s="4" t="s">
-        <v>467</v>
+        <v>260</v>
       </c>
       <c r="C361" s="4"/>
       <c r="D361" s="4">
-        <v>40</v>
+        <v>7500</v>
       </c>
       <c r="E361" s="6"/>
       <c r="F361" s="6"/>
@@ -10236,14 +10202,14 @@
     </row>
     <row r="362" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A362" s="4" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="B362" s="4" t="s">
-        <v>633</v>
+        <v>262</v>
       </c>
       <c r="C362" s="4"/>
       <c r="D362" s="4">
-        <v>4000</v>
+        <v>2000</v>
       </c>
       <c r="E362" s="6"/>
       <c r="F362" s="6"/>
@@ -10253,14 +10219,14 @@
     </row>
     <row r="363" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A363" s="4" t="s">
-        <v>255</v>
+        <v>148</v>
       </c>
       <c r="B363" s="4" t="s">
-        <v>256</v>
+        <v>147</v>
       </c>
       <c r="C363" s="4"/>
       <c r="D363" s="4">
-        <v>500</v>
+        <v>5000000</v>
       </c>
       <c r="E363" s="6"/>
       <c r="F363" s="6"/>
@@ -10277,7 +10243,7 @@
       </c>
       <c r="C364" s="4"/>
       <c r="D364" s="4">
-        <v>5000</v>
+        <v>3000</v>
       </c>
       <c r="E364" s="6"/>
       <c r="F364" s="6"/>
@@ -10285,76 +10251,8 @@
       <c r="H364" s="6"/>
       <c r="I364" s="6"/>
     </row>
-    <row r="365" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A365" s="4" t="s">
-        <v>259</v>
-      </c>
-      <c r="B365" s="4" t="s">
-        <v>260</v>
-      </c>
-      <c r="C365" s="4"/>
-      <c r="D365" s="4">
-        <v>7500</v>
-      </c>
-      <c r="E365" s="6"/>
-      <c r="F365" s="6"/>
-      <c r="G365" s="6"/>
-      <c r="H365" s="6"/>
-      <c r="I365" s="6"/>
-    </row>
-    <row r="366" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A366" s="4" t="s">
-        <v>261</v>
-      </c>
-      <c r="B366" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="C366" s="4"/>
-      <c r="D366" s="4">
-        <v>2000</v>
-      </c>
-      <c r="E366" s="6"/>
-      <c r="F366" s="6"/>
-      <c r="G366" s="6"/>
-      <c r="H366" s="6"/>
-      <c r="I366" s="6"/>
-    </row>
-    <row r="367" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A367" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="B367" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="C367" s="4"/>
-      <c r="D367" s="4">
-        <v>5000000</v>
-      </c>
-      <c r="E367" s="6"/>
-      <c r="F367" s="6"/>
-      <c r="G367" s="6"/>
-      <c r="H367" s="6"/>
-      <c r="I367" s="6"/>
-    </row>
-    <row r="368" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A368" s="4" t="s">
-        <v>636</v>
-      </c>
-      <c r="B368" s="4" t="s">
-        <v>637</v>
-      </c>
-      <c r="C368" s="4"/>
-      <c r="D368" s="4">
-        <v>3000</v>
-      </c>
-      <c r="E368" s="6"/>
-      <c r="F368" s="6"/>
-      <c r="G368" s="6"/>
-      <c r="H368" s="6"/>
-      <c r="I368" s="6"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:I213" xr:uid="{A2181453-C22C-4113-B8D2-921D754AC68D}"/>
+  <autoFilter ref="A1:I209" xr:uid="{A2181453-C22C-4113-B8D2-921D754AC68D}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -10410,7 +10308,7 @@
         <v>473</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
@@ -10479,13 +10377,13 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B6" s="4" t="s">
+        <v>591</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>592</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>593</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
@@ -10511,13 +10409,13 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
+        <v>514</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>516</v>
+      </c>
+      <c r="C7" s="4" t="s">
         <v>515</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>517</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>516</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="4"/>
@@ -10543,13 +10441,13 @@
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>2</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="4"/>
@@ -10607,13 +10505,13 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>5</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
@@ -10745,7 +10643,7 @@
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>10</v>
@@ -10841,13 +10739,13 @@
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>10</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="4"/>
@@ -10973,13 +10871,13 @@
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A21" s="4" t="s">
+        <v>511</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>513</v>
+      </c>
+      <c r="C21" s="4" t="s">
         <v>512</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>514</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>513</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="4"/>
@@ -11011,7 +10909,7 @@
         <v>13</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="4"/>
@@ -11037,13 +10935,13 @@
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A23" s="4" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>13</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="4"/>
@@ -11101,13 +10999,13 @@
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A25" s="4" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>270</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="4"/>
@@ -11133,13 +11031,13 @@
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A26" s="4" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>16</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="4"/>
@@ -11645,13 +11543,13 @@
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A42" s="4" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B42" s="4" t="s">
         <v>38</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="D42" s="4"/>
       <c r="E42" s="4"/>
@@ -11837,7 +11735,7 @@
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A48" s="4" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B48" s="4" t="s">
         <v>40</v>
@@ -12129,7 +12027,7 @@
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A57" s="4" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B57" s="4" t="s">
         <v>58</v>
@@ -12161,13 +12059,13 @@
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A58" s="4" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B58" s="4" t="s">
         <v>58</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D58" s="4"/>
       <c r="E58" s="4"/>
@@ -12199,7 +12097,7 @@
         <v>58</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="D59" s="4"/>
       <c r="E59" s="4" t="s">
@@ -12323,7 +12221,7 @@
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A63" s="4" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="B63" s="4" t="s">
         <v>66</v>
@@ -12581,7 +12479,7 @@
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A71" s="4" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B71" s="4" t="s">
         <v>80</v>
@@ -12709,7 +12607,7 @@
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A75" s="4" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B75" s="4" t="s">
         <v>82</v>
@@ -12783,7 +12681,7 @@
       </c>
       <c r="D77" s="4"/>
       <c r="E77" s="4" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="F77" s="4"/>
       <c r="G77" s="4">
@@ -12903,13 +12801,13 @@
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A81" s="4" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B81" s="4" t="s">
         <v>89</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="D81" s="4"/>
       <c r="E81" s="4"/>
@@ -12977,7 +12875,7 @@
       </c>
       <c r="D83" s="4"/>
       <c r="E83" s="4" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="F83" s="4"/>
       <c r="G83" s="4">
@@ -13011,7 +12909,7 @@
       </c>
       <c r="D84" s="4"/>
       <c r="E84" s="4" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="F84" s="4"/>
       <c r="G84" s="4">
@@ -13099,17 +12997,17 @@
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A87" s="4" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B87" s="4" t="s">
         <v>93</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="D87" s="4"/>
       <c r="E87" s="4" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="F87" s="4"/>
       <c r="G87" s="4">
@@ -13133,17 +13031,17 @@
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A88" s="4" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B88" s="4" t="s">
         <v>93</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="D88" s="4"/>
       <c r="E88" s="4" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="F88" s="4"/>
       <c r="G88" s="4">
@@ -13167,17 +13065,17 @@
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A89" s="4" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B89" s="4" t="s">
         <v>93</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="D89" s="4"/>
       <c r="E89" s="4" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="F89" s="4"/>
       <c r="G89" s="4">
@@ -13555,17 +13453,17 @@
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A101" s="4" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B101" s="4" t="s">
         <v>111</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="D101" s="4"/>
       <c r="E101" s="4" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="F101" s="4"/>
       <c r="G101" s="4">
@@ -13589,13 +13487,13 @@
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A102" s="4" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B102" s="4" t="s">
         <v>112</v>
       </c>
       <c r="C102" s="4" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D102" s="4"/>
       <c r="E102" s="4" t="s">
@@ -13633,7 +13531,7 @@
       </c>
       <c r="D103" s="4"/>
       <c r="E103" s="4" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="F103" s="4"/>
       <c r="G103" s="4">
@@ -13753,7 +13651,7 @@
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A107" s="4" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B107" s="4" t="s">
         <v>119</v>
@@ -14041,13 +13939,13 @@
     </row>
     <row r="116" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A116" s="4" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B116" s="4" t="s">
         <v>131</v>
       </c>
       <c r="C116" s="4" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="D116" s="4"/>
       <c r="E116" s="4"/>
@@ -14553,13 +14451,13 @@
     </row>
     <row r="132" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A132" s="4" t="s">
+        <v>557</v>
+      </c>
+      <c r="B132" s="4" t="s">
+        <v>559</v>
+      </c>
+      <c r="C132" s="4" t="s">
         <v>558</v>
-      </c>
-      <c r="B132" s="4" t="s">
-        <v>560</v>
-      </c>
-      <c r="C132" s="4" t="s">
-        <v>559</v>
       </c>
       <c r="D132" s="4"/>
       <c r="E132" s="4"/>
@@ -14713,13 +14611,13 @@
     </row>
     <row r="137" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A137" s="4" t="s">
+        <v>560</v>
+      </c>
+      <c r="B137" s="4" t="s">
+        <v>562</v>
+      </c>
+      <c r="C137" s="4" t="s">
         <v>561</v>
-      </c>
-      <c r="B137" s="4" t="s">
-        <v>563</v>
-      </c>
-      <c r="C137" s="4" t="s">
-        <v>562</v>
       </c>
       <c r="D137" s="4"/>
       <c r="E137" s="4"/>
@@ -14811,13 +14709,13 @@
     </row>
     <row r="140" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A140" s="4" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B140" s="4" t="s">
         <v>166</v>
       </c>
       <c r="C140" s="4" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="D140" s="4"/>
       <c r="E140" s="4"/>
@@ -14843,13 +14741,13 @@
     </row>
     <row r="141" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A141" s="4" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B141" s="4" t="s">
         <v>167</v>
       </c>
       <c r="C141" s="4" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="D141" s="4"/>
       <c r="E141" s="4"/>
@@ -14971,13 +14869,13 @@
     </row>
     <row r="145" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A145" s="4" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B145" s="4" t="s">
         <v>172</v>
       </c>
       <c r="C145" s="4" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="D145" s="4"/>
       <c r="E145" s="4"/>
@@ -15035,13 +14933,13 @@
     </row>
     <row r="147" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A147" s="4" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="B147" s="4" t="s">
         <v>175</v>
       </c>
       <c r="C147" s="4" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="D147" s="4"/>
       <c r="E147" s="4"/>
@@ -15195,13 +15093,13 @@
     </row>
     <row r="152" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A152" s="4" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B152" s="4" t="s">
         <v>179</v>
       </c>
       <c r="C152" s="4" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="D152" s="4"/>
       <c r="E152" s="4"/>
@@ -15387,13 +15285,13 @@
     </row>
     <row r="158" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A158" s="4" t="s">
+        <v>572</v>
+      </c>
+      <c r="B158" s="4" t="s">
         <v>573</v>
       </c>
-      <c r="B158" s="4" t="s">
-        <v>574</v>
-      </c>
       <c r="C158" s="4" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="D158" s="4"/>
       <c r="E158" s="4"/>
@@ -15419,13 +15317,13 @@
     </row>
     <row r="159" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A159" s="4" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B159" s="4" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="C159" s="4" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="D159" s="4"/>
       <c r="E159" s="4"/>
@@ -15483,13 +15381,13 @@
     </row>
     <row r="161" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A161" s="4" t="s">
+        <v>570</v>
+      </c>
+      <c r="B161" s="4" t="s">
         <v>571</v>
       </c>
-      <c r="B161" s="4" t="s">
-        <v>572</v>
-      </c>
       <c r="C161" s="4" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="D161" s="4"/>
       <c r="E161" s="4"/>
@@ -15515,13 +15413,13 @@
     </row>
     <row r="162" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A162" s="4" t="s">
+        <v>565</v>
+      </c>
+      <c r="B162" s="4" t="s">
+        <v>567</v>
+      </c>
+      <c r="C162" s="4" t="s">
         <v>566</v>
-      </c>
-      <c r="B162" s="4" t="s">
-        <v>568</v>
-      </c>
-      <c r="C162" s="4" t="s">
-        <v>567</v>
       </c>
       <c r="D162" s="4"/>
       <c r="E162" s="4"/>
@@ -15547,13 +15445,13 @@
     </row>
     <row r="163" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A163" s="4" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B163" s="4" t="s">
         <v>192</v>
       </c>
       <c r="C163" s="4" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="D163" s="4"/>
       <c r="E163" s="4"/>
@@ -15643,13 +15541,13 @@
     </row>
     <row r="166" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A166" s="4" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B166" s="4" t="s">
         <v>193</v>
       </c>
       <c r="C166" s="4" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="D166" s="4"/>
       <c r="E166" s="4"/>
@@ -15867,13 +15765,13 @@
     </row>
     <row r="173" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A173" s="4" t="s">
+        <v>582</v>
+      </c>
+      <c r="B173" s="4" t="s">
+        <v>584</v>
+      </c>
+      <c r="C173" s="4" t="s">
         <v>583</v>
-      </c>
-      <c r="B173" s="4" t="s">
-        <v>585</v>
-      </c>
-      <c r="C173" s="4" t="s">
-        <v>584</v>
       </c>
       <c r="D173" s="4"/>
       <c r="E173" s="4"/>
@@ -15899,13 +15797,13 @@
     </row>
     <row r="174" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A174" s="4" t="s">
+        <v>576</v>
+      </c>
+      <c r="B174" s="4" t="s">
+        <v>578</v>
+      </c>
+      <c r="C174" s="4" t="s">
         <v>577</v>
-      </c>
-      <c r="B174" s="4" t="s">
-        <v>579</v>
-      </c>
-      <c r="C174" s="4" t="s">
-        <v>578</v>
       </c>
       <c r="D174" s="4"/>
       <c r="E174" s="4"/>
@@ -15931,13 +15829,13 @@
     </row>
     <row r="175" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A175" s="4" t="s">
+        <v>579</v>
+      </c>
+      <c r="B175" s="4" t="s">
+        <v>581</v>
+      </c>
+      <c r="C175" s="4" t="s">
         <v>580</v>
-      </c>
-      <c r="B175" s="4" t="s">
-        <v>582</v>
-      </c>
-      <c r="C175" s="4" t="s">
-        <v>581</v>
       </c>
       <c r="D175" s="4"/>
       <c r="E175" s="4"/>
@@ -16283,13 +16181,13 @@
     </row>
     <row r="186" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A186" s="4" t="s">
+        <v>585</v>
+      </c>
+      <c r="B186" s="4" t="s">
+        <v>587</v>
+      </c>
+      <c r="C186" s="4" t="s">
         <v>586</v>
-      </c>
-      <c r="B186" s="4" t="s">
-        <v>588</v>
-      </c>
-      <c r="C186" s="4" t="s">
-        <v>587</v>
       </c>
       <c r="D186" s="4"/>
       <c r="E186" s="4"/>
